--- a/data/leagues/Family Fantasy 2026.xlsx
+++ b/data/leagues/Family Fantasy 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="110">
   <si>
     <t>Noah's Nifty Team</t>
   </si>
@@ -61,10 +61,16 @@
     <t>That movie was great...</t>
   </si>
   <si>
-    <t>1-0-0</t>
-  </si>
-  <si>
-    <t>0-1-0</t>
+    <t>2-0-0</t>
+  </si>
+  <si>
+    <t>1-1-0</t>
+  </si>
+  <si>
+    <t>0-2-0</t>
+  </si>
+  <si>
+    <t>0-1-1</t>
   </si>
   <si>
     <t>Teams</t>
@@ -130,6 +136,9 @@
     <t>Week_2</t>
   </si>
   <si>
+    <t>Week_3</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -154,39 +163,39 @@
     <t>Jordan Wallach</t>
   </si>
   <si>
+    <t>Jackson Jansorn</t>
+  </si>
+  <si>
+    <t>Kari Dickert</t>
+  </si>
+  <si>
+    <t>Zach Wallach</t>
+  </si>
+  <si>
+    <t>D Swizzle</t>
+  </si>
+  <si>
+    <t>Gabe Musty</t>
+  </si>
+  <si>
+    <t>Michael Dickert</t>
+  </si>
+  <si>
     <t>lawrence wallach</t>
   </si>
   <si>
-    <t>Gabe Musty</t>
-  </si>
-  <si>
-    <t>Kari Dickert</t>
-  </si>
-  <si>
-    <t>D Swizzle</t>
-  </si>
-  <si>
     <t>Louis Rodriguez</t>
   </si>
   <si>
-    <t>Jackson Jansorn</t>
-  </si>
-  <si>
     <t>Diana Wallach</t>
   </si>
   <si>
+    <t>Ted Wallach</t>
+  </si>
+  <si>
     <t>Noah Wallach</t>
   </si>
   <si>
-    <t>Zach Wallach</t>
-  </si>
-  <si>
-    <t>Ted Wallach</t>
-  </si>
-  <si>
-    <t>Michael Dickert</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -211,67 +220,70 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>12.1-1.8-0.1</t>
-  </si>
-  <si>
-    <t>11.1-2.8-0.1</t>
-  </si>
-  <si>
-    <t>10.7-3.2-0.1</t>
-  </si>
-  <si>
-    <t>10.2-3.7-0.1</t>
-  </si>
-  <si>
-    <t>8.0-6.0-0.1</t>
-  </si>
-  <si>
-    <t>6.1-7.8-0.1</t>
-  </si>
-  <si>
-    <t>5.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>4.4-9.5-0.1</t>
-  </si>
-  <si>
-    <t>3.9-10.0-0.1</t>
-  </si>
-  <si>
-    <t>3.3-10.7-0.1</t>
-  </si>
-  <si>
-    <t>2.3-11.7-0.1</t>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>12.6-1.3</t>
+  </si>
+  <si>
+    <t>11.6-2.3-0.1</t>
+  </si>
+  <si>
+    <t>8.3-5.7</t>
+  </si>
+  <si>
+    <t>8.0-5.9-0.1</t>
+  </si>
+  <si>
+    <t>7.4-6.5-0.1</t>
+  </si>
+  <si>
+    <t>7.6-6.3-0.1</t>
+  </si>
+  <si>
+    <t>7.0-6.8-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.0-0.1</t>
+  </si>
+  <si>
+    <t>5.2-8.7-0.1</t>
+  </si>
+  <si>
+    <t>1.5-12.5-0.1</t>
+  </si>
+  <si>
+    <t>1.7-12.3-0.1</t>
+  </si>
+  <si>
+    <t>13-1</t>
   </si>
   <si>
     <t>12-2</t>
   </si>
   <si>
-    <t>11-3</t>
-  </si>
-  <si>
     <t>8-6</t>
   </si>
   <si>
+    <t>7-7</t>
+  </si>
+  <si>
     <t>6-8</t>
   </si>
   <si>
     <t>5-9</t>
   </si>
   <si>
-    <t>4-10</t>
-  </si>
-  <si>
-    <t>3-11</t>
-  </si>
-  <si>
-    <t>2-12</t>
+    <t>1-13</t>
   </si>
   <si>
     <t>Owners</t>
@@ -283,7 +295,43 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑9</t>
+  </si>
+  <si>
+    <t>↑7</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↓9</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓11</t>
+  </si>
+  <si>
     <t>Week 1</t>
+  </si>
+  <si>
+    <t>Week 2</t>
   </si>
   <si>
     <t>Week</t>
@@ -749,22 +797,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
         <v>13</v>
@@ -773,13 +821,13 @@
         <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M3" t="s">
         <v>13</v>
@@ -790,7 +838,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -799,13 +847,13 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
         <v>13</v>
@@ -814,13 +862,13 @@
         <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M4" t="s">
         <v>13</v>
@@ -831,37 +879,37 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M5" t="s">
         <v>13</v>
@@ -872,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -881,7 +929,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -896,13 +944,13 @@
         <v>13</v>
       </c>
       <c r="J6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6" t="s">
         <v>12</v>
       </c>
       <c r="L6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6" t="s">
         <v>13</v>
@@ -943,7 +991,7 @@
         <v>12</v>
       </c>
       <c r="L7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7" t="s">
         <v>13</v>
@@ -978,13 +1026,13 @@
         <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" t="s">
         <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M8" t="s">
         <v>12</v>
@@ -995,40 +1043,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1036,22 +1084,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
         <v>12</v>
@@ -1060,13 +1108,13 @@
         <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M10" t="s">
         <v>12</v>
@@ -1077,37 +1125,37 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I11" t="s">
         <v>12</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" t="s">
         <v>12</v>
@@ -1118,7 +1166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -1127,7 +1175,7 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -1142,13 +1190,13 @@
         <v>13</v>
       </c>
       <c r="J12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K12" t="s">
         <v>12</v>
       </c>
       <c r="L12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" t="s">
         <v>12</v>
@@ -1159,37 +1207,37 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I13" t="s">
         <v>12</v>
       </c>
       <c r="J13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M13" t="s">
         <v>12</v>
@@ -1202,30 +1250,56 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>-7</v>
+      </c>
+      <c r="G2">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1240,13 +1314,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1254,13 +1328,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>0.08333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1268,13 +1342,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.1666666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1282,13 +1356,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>0.25</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1296,10 +1370,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>0.3333333333333333</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -1310,10 +1384,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.4166666666666667</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -1324,10 +1398,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>0.4166666666666667</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -1338,10 +1412,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1352,13 +1426,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>0.6666666666666666</v>
+        <v>1.25</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1366,13 +1440,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>0.6666666666666666</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1380,13 +1454,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C11">
-        <v>0.75</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1394,10 +1468,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>0.8333333333333334</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
@@ -1408,10 +1482,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>0.9166666666666666</v>
+        <v>1.5</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
@@ -1429,16 +1503,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1446,13 +1520,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.08333333333333326</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1463,13 +1537,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>0.9166666666666666</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D3">
-        <v>-0.08333333333333337</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1480,13 +1554,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>0.8333333333333334</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D4">
-        <v>-0.1666666666666666</v>
+        <v>-0.8333333333333333</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
@@ -1497,16 +1571,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>0.75</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D5">
-        <v>-0.25</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1514,16 +1588,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D6">
-        <v>-0.3333333333333334</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1531,16 +1605,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="D7">
-        <v>0.5</v>
+        <v>-0.9166666666666667</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1548,16 +1622,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>0.4166666666666667</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="D8">
-        <v>-0.5833333333333333</v>
+        <v>0.08333333333333326</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1565,13 +1639,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>0.4166666666666667</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D9">
-        <v>0.4166666666666667</v>
+        <v>-0.08333333333333337</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -1582,16 +1656,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="D10">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1602,10 +1676,10 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>0.1666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D11">
-        <v>0.1666666666666667</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -1616,16 +1690,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>0.08333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D12">
-        <v>0.08333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1633,16 +1707,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1657,69 +1731,69 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>61.4</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="C2">
-        <v>22.4</v>
+        <v>19.1</v>
       </c>
       <c r="D2">
-        <v>12.1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="F2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1745,28 +1819,28 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="C3">
-        <v>34.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D3">
-        <v>25.4</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>16.7</v>
+        <v>1.4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="G3">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1784,86 +1858,86 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>11.7</v>
+        <v>0.9</v>
       </c>
       <c r="C4">
-        <v>24.8</v>
+        <v>6.5</v>
       </c>
       <c r="D4">
-        <v>32.5</v>
+        <v>26.1</v>
       </c>
       <c r="E4">
-        <v>23.4</v>
+        <v>17.7</v>
       </c>
       <c r="F4">
-        <v>6.6</v>
+        <v>14.2</v>
       </c>
       <c r="G4">
-        <v>0.8</v>
+        <v>9.9</v>
       </c>
       <c r="H4">
-        <v>0.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N4">
-        <v>99.8</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>17.8</v>
+        <v>2.8</v>
       </c>
       <c r="D5">
-        <v>26.2</v>
+        <v>17.6</v>
       </c>
       <c r="E5">
-        <v>38.8</v>
+        <v>19.6</v>
       </c>
       <c r="F5">
-        <v>8.300000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="G5">
-        <v>1.9</v>
+        <v>15.6</v>
       </c>
       <c r="H5">
-        <v>0.5</v>
+        <v>12.9</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1872,183 +1946,183 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>99.40000000000001</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>11.6</v>
       </c>
       <c r="E6">
-        <v>12.5</v>
+        <v>19.2</v>
       </c>
       <c r="F6">
-        <v>46.9</v>
+        <v>18.9</v>
       </c>
       <c r="G6">
-        <v>22.6</v>
+        <v>17.8</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="I6">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="J6">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="K6">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="L6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>86.09999999999999</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>0.4</v>
+        <v>18.4</v>
       </c>
       <c r="E7">
-        <v>1.7</v>
+        <v>16.4</v>
       </c>
       <c r="F7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="G7">
-        <v>25.6</v>
+        <v>14.4</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>11.7</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>9.5</v>
       </c>
       <c r="J7">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="K7">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="M7">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>42</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D8">
-        <v>0.3</v>
+        <v>5.4</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>12.4</v>
       </c>
       <c r="F8">
-        <v>13.2</v>
+        <v>16.1</v>
       </c>
       <c r="G8">
-        <v>26.3</v>
+        <v>16.4</v>
       </c>
       <c r="H8">
-        <v>22.8</v>
+        <v>19.9</v>
       </c>
       <c r="I8">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="K8">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="L8">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>41.8</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D9">
-        <v>0.1</v>
+        <v>8.1</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>10.4</v>
       </c>
       <c r="F9">
-        <v>4.7</v>
+        <v>11.7</v>
       </c>
       <c r="G9">
         <v>12.6</v>
       </c>
       <c r="H9">
-        <v>17.8</v>
+        <v>11.7</v>
       </c>
       <c r="I9">
-        <v>25.6</v>
+        <v>15.3</v>
       </c>
       <c r="J9">
-        <v>18.1</v>
+        <v>13.7</v>
       </c>
       <c r="K9">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="L9">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="M9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>18.4</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2062,42 +2136,42 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E10">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="F10">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="G10">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="H10">
-        <v>11.9</v>
+        <v>13.5</v>
       </c>
       <c r="I10">
-        <v>16.2</v>
+        <v>18.8</v>
       </c>
       <c r="J10">
-        <v>22.8</v>
+        <v>25.5</v>
       </c>
       <c r="K10">
-        <v>20.1</v>
+        <v>26.8</v>
       </c>
       <c r="L10">
-        <v>13.9</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <v>7.8</v>
+        <v>0.1</v>
       </c>
       <c r="N10">
-        <v>7.3</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2106,42 +2180,42 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F11">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="G11">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="H11">
-        <v>7.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I11">
-        <v>14</v>
+        <v>15.3</v>
       </c>
       <c r="J11">
-        <v>19.4</v>
+        <v>27.7</v>
       </c>
       <c r="K11">
-        <v>26.1</v>
+        <v>37.2</v>
       </c>
       <c r="L11">
-        <v>19.9</v>
+        <v>1.4</v>
       </c>
       <c r="M11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2156,36 +2230,36 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>17.7</v>
+        <v>1.6</v>
       </c>
       <c r="L12">
-        <v>33.1</v>
+        <v>50.6</v>
       </c>
       <c r="M12">
-        <v>23.3</v>
+        <v>47.8</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2200,31 +2274,31 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>5.5</v>
+        <v>0.2</v>
       </c>
       <c r="K13">
-        <v>11.1</v>
+        <v>2.3</v>
       </c>
       <c r="L13">
-        <v>24</v>
+        <v>45.5</v>
       </c>
       <c r="M13">
-        <v>57.3</v>
+        <v>52</v>
       </c>
       <c r="N13">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2234,147 +2308,186 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="C4">
-        <v>99.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>79.3</v>
+      </c>
+      <c r="D4">
+        <v>75.90000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>23.3</v>
+      </c>
+      <c r="C5">
+        <v>74.3</v>
+      </c>
+      <c r="D5">
+        <v>73.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>38.9</v>
+      </c>
+      <c r="C6">
+        <v>58.5</v>
+      </c>
+      <c r="D6">
+        <v>67.10000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>67.10000000000001</v>
+      </c>
+      <c r="D7">
+        <v>64.09999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>87.3</v>
+      </c>
+      <c r="C8">
+        <v>48.5</v>
+      </c>
+      <c r="D8">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>99.8</v>
-      </c>
-      <c r="C5">
-        <v>99.40000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>88.8</v>
-      </c>
-      <c r="C6">
-        <v>85.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>37.9</v>
-      </c>
-      <c r="C7">
-        <v>42.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>36.1</v>
-      </c>
-      <c r="C8">
-        <v>39.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B9">
-        <v>23.9</v>
+        <v>100</v>
       </c>
       <c r="C9">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>43.5</v>
+      </c>
+      <c r="D9">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B10">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C10">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>14.8</v>
+      </c>
+      <c r="D10">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B11">
+        <v>34.59999999999999</v>
+      </c>
+      <c r="C11">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C11">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
+      <c r="B12">
+        <v>0.1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B12">
-        <v>1.3</v>
-      </c>
-      <c r="C12">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="B13">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="C13">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2389,28 +2502,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2421,25 +2534,25 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D2">
-        <v>84.45999999999999</v>
+        <v>86.98</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>129.82</v>
+        <v>123.3</v>
       </c>
       <c r="G2">
-        <v>0.615</v>
+        <v>0.583</v>
       </c>
       <c r="H2">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2447,28 +2560,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D3">
-        <v>100.32</v>
+        <v>116.37</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
       </c>
       <c r="F3">
-        <v>120.91</v>
+        <v>120.4</v>
       </c>
       <c r="G3">
-        <v>0.462</v>
+        <v>0.542</v>
       </c>
       <c r="H3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2476,28 +2589,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D4">
-        <v>104.32</v>
+        <v>118.28</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>124.96</v>
+        <v>118.54</v>
       </c>
       <c r="G4">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="H4">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2505,28 +2618,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D5">
-        <v>123.9</v>
+        <v>124.49</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5">
-        <v>120.2</v>
+        <v>117.91</v>
       </c>
       <c r="G5">
-        <v>0.385</v>
+        <v>0.458</v>
       </c>
       <c r="H5">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2537,25 +2650,25 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D6">
-        <v>92.06</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>126.15</v>
+        <v>119.69</v>
       </c>
       <c r="G6">
-        <v>0.538</v>
+        <v>0.542</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2563,28 +2676,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <v>101.76</v>
+        <v>117.47</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>127.22</v>
+        <v>117.56</v>
       </c>
       <c r="G7">
-        <v>0.615</v>
+        <v>0.417</v>
       </c>
       <c r="H7">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2592,28 +2705,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>148.66</v>
+        <v>112.89</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>120.98</v>
+        <v>118.32</v>
       </c>
       <c r="G8">
-        <v>0.538</v>
+        <v>0.583</v>
       </c>
       <c r="H8">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2621,28 +2734,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D9">
-        <v>119.96</v>
+        <v>106.49</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
       </c>
       <c r="F9">
-        <v>124.9</v>
+        <v>116.18</v>
       </c>
       <c r="G9">
-        <v>0.615</v>
+        <v>0.458</v>
       </c>
       <c r="H9">
-        <v>-0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2650,28 +2763,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D10">
-        <v>154.96</v>
+        <v>124.1</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>116.48</v>
+        <v>117.97</v>
       </c>
       <c r="G10">
-        <v>0.385</v>
+        <v>0.542</v>
       </c>
       <c r="H10">
-        <v>-0.3</v>
+        <v>-0.8</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2679,28 +2792,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D11">
-        <v>166.86</v>
+        <v>125.49</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11">
-        <v>114.75</v>
+        <v>117.34</v>
       </c>
       <c r="G11">
-        <v>0.385</v>
+        <v>0.542</v>
       </c>
       <c r="H11">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2711,25 +2824,25 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D12">
-        <v>152.3</v>
+        <v>145.94</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
       <c r="F12">
-        <v>118.9</v>
+        <v>115.47</v>
       </c>
       <c r="G12">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="H12">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="I12">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2737,28 +2850,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D13">
-        <v>115.26</v>
+        <v>151.32</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>119.55</v>
+        <v>112.58</v>
       </c>
       <c r="G13">
-        <v>0.538</v>
+        <v>0.417</v>
       </c>
       <c r="H13">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="I13">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2773,48 +2886,48 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>166.86</v>
+        <v>151.32</v>
       </c>
       <c r="E2">
-        <v>166.86</v>
+        <v>302.64</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2823,213 +2936,213 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>154.96</v>
+        <v>145.94</v>
       </c>
       <c r="E3">
-        <v>154.96</v>
+        <v>291.88</v>
       </c>
       <c r="F3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>152.3</v>
+        <v>124.49</v>
       </c>
       <c r="E4">
-        <v>152.3</v>
+        <v>248.98</v>
       </c>
       <c r="F4">
-        <v>99.8</v>
+        <v>75.3</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>148.66</v>
+        <v>117.47</v>
       </c>
       <c r="E5">
-        <v>148.66</v>
+        <v>234.94</v>
       </c>
       <c r="F5">
-        <v>99.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>123.9</v>
+        <v>125.49</v>
       </c>
       <c r="E6">
-        <v>123.9</v>
+        <v>250.98</v>
       </c>
       <c r="F6">
-        <v>86.09999999999999</v>
+        <v>68.10000000000001</v>
       </c>
       <c r="G6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>119.96</v>
+        <v>124.1</v>
       </c>
       <c r="E7">
-        <v>119.96</v>
+        <v>248.2</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G7">
-        <v>0.7000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>115.26</v>
+        <v>118.28</v>
       </c>
       <c r="E8">
-        <v>115.26</v>
+        <v>236.56</v>
       </c>
       <c r="F8">
-        <v>41.8</v>
+        <v>50.4</v>
       </c>
       <c r="G8">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>104.32</v>
+        <v>116.37</v>
       </c>
       <c r="E9">
-        <v>104.32</v>
+        <v>232.74</v>
       </c>
       <c r="F9">
-        <v>18.4</v>
+        <v>43.7</v>
       </c>
       <c r="G9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3037,115 +3150,115 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>100.32</v>
+        <v>106.49</v>
       </c>
       <c r="E10">
-        <v>100.32</v>
+        <v>212.98</v>
       </c>
       <c r="F10">
-        <v>7.3</v>
+        <v>14.3</v>
       </c>
       <c r="G10">
-        <v>7.8</v>
+        <v>0.1</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I10" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>101.76</v>
+        <v>112.89</v>
       </c>
       <c r="E11">
-        <v>101.76</v>
+        <v>225.78</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>9.1</v>
       </c>
       <c r="G11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>92.06</v>
+        <v>86.97999999999999</v>
       </c>
       <c r="E12">
-        <v>92.06</v>
+        <v>173.96</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>23.3</v>
+        <v>47.8</v>
       </c>
       <c r="H12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>84.45999999999999</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="E13">
-        <v>84.45999999999999</v>
+        <v>170.86</v>
       </c>
       <c r="F13">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>57.3</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -3160,19 +3273,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3180,19 +3293,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="F2">
-        <v>0</v>
+      <c r="F2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3200,19 +3313,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3220,19 +3333,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3240,19 +3353,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3260,19 +3373,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3280,7 +3393,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>47</v>
@@ -3291,8 +3404,8 @@
       <c r="E7" t="s">
         <v>13</v>
       </c>
-      <c r="F7">
-        <v>0</v>
+      <c r="F7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3300,19 +3413,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
       </c>
-      <c r="F8">
-        <v>0</v>
+      <c r="F8" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3320,19 +3433,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3340,19 +3453,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D10">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
       </c>
-      <c r="F10">
-        <v>0</v>
+      <c r="F10" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3363,16 +3476,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D11">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
-      <c r="F11">
-        <v>0</v>
+      <c r="F11" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3380,19 +3493,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D12">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
       </c>
-      <c r="F12">
-        <v>0</v>
+      <c r="F12" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3400,19 +3513,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D13">
-        <v>-6</v>
+        <v>-15</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -3422,117 +3535,147 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>102</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>-2</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
+      <c r="B8">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
+      <c r="C8">
+        <v>-3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
+      <c r="B9">
+        <v>-4</v>
+      </c>
+      <c r="C9">
+        <v>-4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
         <v>-2</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>-2</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>-4</v>
-      </c>
       <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>-5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -3540,29 +3683,38 @@
         <v>-4</v>
       </c>
       <c r="C11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>-5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>-6</v>
+      </c>
+      <c r="C12">
+        <v>-7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>-4</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13">
-        <v>-6</v>
-      </c>
       <c r="C13">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Family Fantasy 2026.xlsx
+++ b/data/leagues/Family Fantasy 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="111">
   <si>
     <t>Noah's Nifty Team</t>
   </si>
@@ -229,7 +229,7 @@
     <t>1-1</t>
   </si>
   <si>
-    <t>12.6-1.3</t>
+    <t>12.6-1.4</t>
   </si>
   <si>
     <t>11.6-2.3-0.1</t>
@@ -244,25 +244,25 @@
     <t>7.4-6.5-0.1</t>
   </si>
   <si>
-    <t>7.6-6.3-0.1</t>
-  </si>
-  <si>
-    <t>7.0-6.8-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.2-0.1</t>
+    <t>7.5-6.4-0.1</t>
+  </si>
+  <si>
+    <t>7.0-6.9-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.3-0.1</t>
   </si>
   <si>
     <t>5.9-8.0-0.1</t>
   </si>
   <si>
-    <t>5.2-8.7-0.1</t>
-  </si>
-  <si>
-    <t>1.5-12.5-0.1</t>
-  </si>
-  <si>
-    <t>1.7-12.3-0.1</t>
+    <t>5.3-8.5-0.1</t>
+  </si>
+  <si>
+    <t>1.6-12.4</t>
+  </si>
+  <si>
+    <t>1.7-12.2-0.1</t>
   </si>
   <si>
     <t>13-1</t>
@@ -271,6 +271,9 @@
     <t>12-2</t>
   </si>
   <si>
+    <t>9-5</t>
+  </si>
+  <si>
     <t>8-6</t>
   </si>
   <si>
@@ -283,7 +286,7 @@
     <t>5-9</t>
   </si>
   <si>
-    <t>1-13</t>
+    <t>2-12</t>
   </si>
   <si>
     <t>Owners</t>
@@ -1255,25 +1258,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1778,16 +1781,16 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>78.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="C2">
-        <v>19.1</v>
+        <v>21.4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E2">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1822,22 +1825,22 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>20.2</v>
+        <v>21.1</v>
       </c>
       <c r="C3">
-        <v>68.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="E3">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F3">
+        <v>0.3</v>
+      </c>
+      <c r="G3">
         <v>0.1</v>
-      </c>
-      <c r="G3">
-        <v>0.2</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1866,43 +1869,43 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="C4">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D4">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>17.7</v>
+        <v>18.5</v>
       </c>
       <c r="F4">
-        <v>14.2</v>
+        <v>12.8</v>
       </c>
       <c r="G4">
-        <v>9.9</v>
+        <v>10.8</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
-        <v>8.1</v>
+        <v>6.2</v>
       </c>
       <c r="J4">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>75.3</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1910,35 +1913,35 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C5">
+        <v>2.2</v>
+      </c>
+      <c r="D5">
+        <v>18.5</v>
+      </c>
+      <c r="E5">
+        <v>19.1</v>
+      </c>
+      <c r="F5">
+        <v>17.5</v>
+      </c>
+      <c r="G5">
+        <v>14.4</v>
+      </c>
+      <c r="H5">
+        <v>11.6</v>
+      </c>
+      <c r="I5">
+        <v>8.5</v>
+      </c>
+      <c r="J5">
+        <v>5.2</v>
+      </c>
+      <c r="K5">
         <v>2.8</v>
       </c>
-      <c r="D5">
-        <v>17.6</v>
-      </c>
-      <c r="E5">
-        <v>19.6</v>
-      </c>
-      <c r="F5">
-        <v>17.6</v>
-      </c>
-      <c r="G5">
-        <v>15.6</v>
-      </c>
-      <c r="H5">
-        <v>12.9</v>
-      </c>
-      <c r="I5">
-        <v>6.6</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>2.3</v>
-      </c>
       <c r="L5">
         <v>0</v>
       </c>
@@ -1946,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>73.2</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1957,31 +1960,31 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="F6">
-        <v>18.9</v>
+        <v>21.8</v>
       </c>
       <c r="G6">
-        <v>17.8</v>
+        <v>14.7</v>
       </c>
       <c r="H6">
         <v>12.8</v>
       </c>
       <c r="I6">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="K6">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1990,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>68.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1998,43 +2001,43 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D7">
-        <v>18.4</v>
+        <v>17.4</v>
       </c>
       <c r="E7">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="F7">
-        <v>14.5</v>
+        <v>16.9</v>
       </c>
       <c r="G7">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="H7">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="I7">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="J7">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L7">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>65.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -2042,34 +2045,34 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C8">
         <v>0.1</v>
       </c>
       <c r="D8">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="E8">
-        <v>12.4</v>
+        <v>11.2</v>
       </c>
       <c r="F8">
-        <v>16.1</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>16.4</v>
+        <v>18.5</v>
       </c>
       <c r="H8">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="I8">
-        <v>15.8</v>
+        <v>16.6</v>
       </c>
       <c r="J8">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="K8">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2078,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>50.4</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2086,43 +2089,43 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C9">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D9">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="E9">
+        <v>8.9</v>
+      </c>
+      <c r="F9">
         <v>10.4</v>
       </c>
-      <c r="F9">
-        <v>11.7</v>
-      </c>
       <c r="G9">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="H9">
-        <v>11.7</v>
+        <v>12.5</v>
       </c>
       <c r="I9">
-        <v>15.3</v>
+        <v>14.1</v>
       </c>
       <c r="J9">
-        <v>13.7</v>
+        <v>15.6</v>
       </c>
       <c r="K9">
-        <v>14.3</v>
+        <v>15.1</v>
       </c>
       <c r="L9">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>43.7</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2133,40 +2136,40 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D10">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E10">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="G10">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H10">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="I10">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="J10">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="K10">
-        <v>26.8</v>
+        <v>27.9</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M10">
         <v>0.1</v>
       </c>
       <c r="N10">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2180,37 +2183,37 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E11">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="F11">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="G11">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="H11">
-        <v>9.300000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="I11">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="J11">
-        <v>27.7</v>
+        <v>24.5</v>
       </c>
       <c r="K11">
-        <v>37.2</v>
+        <v>33.9</v>
       </c>
       <c r="L11">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N11">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2242,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K12">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="L12">
-        <v>50.6</v>
+        <v>51.5</v>
       </c>
       <c r="M12">
-        <v>47.8</v>
+        <v>47.2</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2286,16 +2289,16 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K13">
         <v>2.3</v>
       </c>
       <c r="L13">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="M13">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2327,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2341,7 +2344,7 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -2358,10 +2361,10 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>79.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D4">
-        <v>75.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2369,13 +2372,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>74.3</v>
+        <v>72.2</v>
       </c>
       <c r="D5">
-        <v>73.7</v>
+        <v>72.39999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2383,10 +2386,10 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>38.9</v>
+        <v>39.3</v>
       </c>
       <c r="C6">
-        <v>58.5</v>
+        <v>57.09999999999999</v>
       </c>
       <c r="D6">
         <v>67.10000000000001</v>
@@ -2397,13 +2400,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="C7">
-        <v>67.10000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="D7">
-        <v>64.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2411,13 +2414,13 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>87.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C8">
-        <v>48.5</v>
+        <v>50.8</v>
       </c>
       <c r="D8">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2425,13 +2428,13 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="C9">
-        <v>43.5</v>
+        <v>46.1</v>
       </c>
       <c r="D9">
-        <v>44.7</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2439,13 +2442,13 @@
         <v>2</v>
       </c>
       <c r="B10">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="C10">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="D10">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2453,13 +2456,13 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>34.59999999999999</v>
+        <v>35.3</v>
       </c>
       <c r="C11">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="D11">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2481,7 +2484,7 @@
         <v>7</v>
       </c>
       <c r="B13">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2988,10 +2991,10 @@
         <v>248.98</v>
       </c>
       <c r="F4">
-        <v>75.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
         <v>70</v>
@@ -3017,7 +3020,7 @@
         <v>234.94</v>
       </c>
       <c r="F5">
-        <v>73.2</v>
+        <v>71.89999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -3026,7 +3029,7 @@
         <v>71</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3046,7 +3049,7 @@
         <v>250.98</v>
       </c>
       <c r="F6">
-        <v>68.10000000000001</v>
+        <v>68.89999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3055,7 +3058,7 @@
         <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3075,7 +3078,7 @@
         <v>248.2</v>
       </c>
       <c r="F7">
-        <v>65.90000000000001</v>
+        <v>67.60000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -3084,7 +3087,7 @@
         <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3104,7 +3107,7 @@
         <v>236.56</v>
       </c>
       <c r="F8">
-        <v>50.4</v>
+        <v>48.8</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -3113,7 +3116,7 @@
         <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3133,7 +3136,7 @@
         <v>232.74</v>
       </c>
       <c r="F9">
-        <v>43.7</v>
+        <v>41.3</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3142,7 +3145,7 @@
         <v>75</v>
       </c>
       <c r="I9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3162,7 +3165,7 @@
         <v>212.98</v>
       </c>
       <c r="F10">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
       <c r="G10">
         <v>0.1</v>
@@ -3171,7 +3174,7 @@
         <v>76</v>
       </c>
       <c r="I10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3191,16 +3194,16 @@
         <v>225.78</v>
       </c>
       <c r="F11">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H11" t="s">
         <v>77</v>
       </c>
       <c r="I11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3223,13 +3226,13 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>47.8</v>
+        <v>47.2</v>
       </c>
       <c r="H12" t="s">
         <v>78</v>
       </c>
       <c r="I12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3252,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="H13" t="s">
         <v>79</v>
       </c>
       <c r="I13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -3276,16 +3279,16 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3305,7 +3308,7 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3325,7 +3328,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3345,7 +3348,7 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3365,7 +3368,7 @@
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3385,7 +3388,7 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3405,7 +3408,7 @@
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3425,7 +3428,7 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3445,7 +3448,7 @@
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3465,7 +3468,7 @@
         <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3485,7 +3488,7 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3505,7 +3508,7 @@
         <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3525,7 +3528,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3540,13 +3543,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3560,7 +3563,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3574,7 +3577,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3588,7 +3591,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3602,7 +3605,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3616,7 +3619,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3630,7 +3633,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3644,7 +3647,7 @@
         <v>-3</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3658,7 +3661,7 @@
         <v>-4</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3672,7 +3675,7 @@
         <v>-5</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3686,7 +3689,7 @@
         <v>-5</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3700,7 +3703,7 @@
         <v>-7</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3714,7 +3717,7 @@
         <v>-15</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Family Fantasy 2026.xlsx
+++ b/data/leagues/Family Fantasy 2026.xlsx
@@ -23,12 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="116">
   <si>
     <t>Noah's Nifty Team</t>
   </si>
   <si>
-    <t>Michael's Magnificent Team</t>
+    <t>Ragebaiters</t>
   </si>
   <si>
     <t>lawrence's Lucrative Team</t>
@@ -61,16 +61,19 @@
     <t>That movie was great...</t>
   </si>
   <si>
-    <t>2-0-0</t>
-  </si>
-  <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>0-2-0</t>
-  </si>
-  <si>
-    <t>0-1-1</t>
+    <t>3-0-0</t>
+  </si>
+  <si>
+    <t>2-1-0</t>
+  </si>
+  <si>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>0-3-0</t>
+  </si>
+  <si>
+    <t>1-1-1</t>
   </si>
   <si>
     <t>Teams</t>
@@ -139,6 +142,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -160,42 +166,42 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>D Swizzle</t>
+  </si>
+  <si>
+    <t>Zach Wallach</t>
+  </si>
+  <si>
+    <t>Gabe Musty</t>
+  </si>
+  <si>
     <t>Jordan Wallach</t>
   </si>
   <si>
     <t>Jackson Jansorn</t>
   </si>
   <si>
+    <t>Michael Dickert</t>
+  </si>
+  <si>
+    <t>lawrence wallach</t>
+  </si>
+  <si>
+    <t>Louis Rodriguez</t>
+  </si>
+  <si>
     <t>Kari Dickert</t>
   </si>
   <si>
-    <t>Zach Wallach</t>
-  </si>
-  <si>
-    <t>D Swizzle</t>
-  </si>
-  <si>
-    <t>Gabe Musty</t>
-  </si>
-  <si>
-    <t>Michael Dickert</t>
-  </si>
-  <si>
-    <t>lawrence wallach</t>
-  </si>
-  <si>
-    <t>Louis Rodriguez</t>
+    <t>Ted Wallach</t>
+  </si>
+  <si>
+    <t>Noah Wallach</t>
   </si>
   <si>
     <t>Diana Wallach</t>
   </si>
   <si>
-    <t>Ted Wallach</t>
-  </si>
-  <si>
-    <t>Noah Wallach</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -220,57 +226,60 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>12.6-1.4</t>
-  </si>
-  <si>
-    <t>11.6-2.3-0.1</t>
-  </si>
-  <si>
-    <t>8.3-5.7</t>
-  </si>
-  <si>
-    <t>8.0-5.9-0.1</t>
-  </si>
-  <si>
-    <t>7.4-6.5-0.1</t>
-  </si>
-  <si>
-    <t>7.5-6.4-0.1</t>
-  </si>
-  <si>
-    <t>7.0-6.9-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.3-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.0-0.1</t>
-  </si>
-  <si>
-    <t>5.3-8.5-0.1</t>
-  </si>
-  <si>
-    <t>1.6-12.4</t>
-  </si>
-  <si>
-    <t>1.7-12.2-0.1</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>11.8-2.1-0.1</t>
+  </si>
+  <si>
+    <t>12.9-1.1-0.1</t>
+  </si>
+  <si>
+    <t>8.6-5.3-0.1</t>
+  </si>
+  <si>
+    <t>8.7-5.2-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.5-0.1</t>
+  </si>
+  <si>
+    <t>6.4-7.5-0.1</t>
+  </si>
+  <si>
+    <t>6.6-7.3-0.1</t>
+  </si>
+  <si>
+    <t>5.7-8.2-0.1</t>
+  </si>
+  <si>
+    <t>5.3-8.6-0.1</t>
+  </si>
+  <si>
+    <t>4.5-9.4-0.1</t>
+  </si>
+  <si>
+    <t>2.8-11.1-0.1</t>
+  </si>
+  <si>
+    <t>1.8-12.1-0.1</t>
+  </si>
+  <si>
+    <t>12-2</t>
   </si>
   <si>
     <t>13-1</t>
   </si>
   <si>
-    <t>12-2</t>
-  </si>
-  <si>
     <t>9-5</t>
   </si>
   <si>
@@ -298,10 +307,10 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑9</t>
-  </si>
-  <si>
-    <t>↑7</t>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↑1</t>
   </si>
   <si>
     <t>↑2</t>
@@ -310,31 +319,37 @@
     <t>↑6</t>
   </si>
   <si>
+    <t>↓8</t>
+  </si>
+  <si>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>↓2</t>
   </si>
   <si>
+    <t>↓6</t>
+  </si>
+  <si>
     <t>↑3</t>
   </si>
   <si>
-    <t>↓9</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓11</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -786,10 +801,10 @@
         <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M2" t="s">
         <v>12</v>
@@ -803,34 +818,34 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
         <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M3" t="s">
         <v>13</v>
@@ -850,13 +865,13 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
         <v>13</v>
@@ -868,10 +883,10 @@
         <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M4" t="s">
         <v>13</v>
@@ -882,37 +897,37 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M5" t="s">
         <v>13</v>
@@ -929,10 +944,10 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -944,16 +959,16 @@
         <v>13</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M6" t="s">
         <v>13</v>
@@ -964,40 +979,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1052,10 +1067,10 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
@@ -1067,16 +1082,16 @@
         <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" t="s">
         <v>14</v>
       </c>
       <c r="K9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M9" t="s">
         <v>14</v>
@@ -1090,7 +1105,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1114,7 +1129,7 @@
         <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L10" t="s">
         <v>14</v>
@@ -1128,37 +1143,37 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M11" t="s">
         <v>12</v>
@@ -1175,10 +1190,10 @@
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -1190,16 +1205,16 @@
         <v>13</v>
       </c>
       <c r="I12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M12" t="s">
         <v>12</v>
@@ -1213,13 +1228,13 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
@@ -1231,16 +1246,16 @@
         <v>13</v>
       </c>
       <c r="I13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M13" t="s">
         <v>12</v>
@@ -1253,30 +1268,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1303,6 +1318,84 @@
       </c>
       <c r="H2" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>-9</v>
+      </c>
+      <c r="F3">
+        <v>-1</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>14</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>-7</v>
+      </c>
+      <c r="F5">
+        <v>-2</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1317,13 +1410,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1334,10 +1427,10 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1345,13 +1438,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>0.5833333333333334</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1359,13 +1452,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0.5833333333333334</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1376,10 +1469,10 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>0.5833333333333334</v>
+        <v>1.25</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1387,13 +1480,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>0.9166666666666666</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1401,13 +1494,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1415,13 +1508,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>1.083333333333333</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1429,13 +1522,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1.25</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1446,10 +1539,10 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>1.333333333333333</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1457,13 +1550,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>1.333333333333333</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1471,10 +1564,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>1.416666666666667</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
@@ -1485,10 +1578,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>1.5</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
@@ -1506,16 +1599,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1526,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.916666666666667</v>
+        <v>2.75</v>
       </c>
       <c r="D2">
-        <v>-0.08333333333333326</v>
+        <v>-0.25</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1543,10 +1636,10 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>1.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D3">
-        <v>-0.3333333333333333</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1557,16 +1650,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>-0.8333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1574,16 +1667,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>1.166666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D5">
-        <v>0.1666666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1591,16 +1684,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>1.166666666666667</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D6">
-        <v>1.166666666666667</v>
+        <v>-1.416666666666667</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1608,13 +1701,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>1.083333333333333</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D7">
-        <v>-0.9166666666666667</v>
+        <v>-1.416666666666667</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -1625,13 +1718,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>1.083333333333333</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="D8">
-        <v>0.08333333333333326</v>
+        <v>-0.5833333333333333</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
@@ -1642,16 +1735,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>0.9166666666666666</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D9">
-        <v>-0.08333333333333337</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1659,13 +1752,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="C10">
-        <v>0.75</v>
-      </c>
       <c r="D10">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
@@ -1676,16 +1769,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>-0.3333333333333334</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1693,16 +1786,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D12">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1710,16 +1803,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>0.08333333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D13">
-        <v>0.08333333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1734,46 +1827,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1781,19 +1874,19 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>77</v>
+        <v>20.4</v>
       </c>
       <c r="C2">
-        <v>21.4</v>
+        <v>70.3</v>
       </c>
       <c r="D2">
-        <v>1.5</v>
+        <v>7.3</v>
       </c>
       <c r="E2">
+        <v>1.9</v>
+      </c>
+      <c r="F2">
         <v>0.1</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1825,22 +1918,22 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>21.1</v>
+        <v>79</v>
       </c>
       <c r="C3">
-        <v>67.2</v>
+        <v>19.9</v>
       </c>
       <c r="D3">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="F3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1866,310 +1959,310 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>31.4</v>
       </c>
       <c r="E4">
-        <v>18.5</v>
+        <v>27.8</v>
       </c>
       <c r="F4">
-        <v>12.8</v>
+        <v>18.8</v>
       </c>
       <c r="G4">
-        <v>10.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="J4">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="K4">
-        <v>4.2</v>
+        <v>0.3</v>
       </c>
       <c r="L4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>74.90000000000001</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B5">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C5">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="D5">
-        <v>18.5</v>
+        <v>31.7</v>
       </c>
       <c r="E5">
-        <v>19.1</v>
+        <v>24.2</v>
       </c>
       <c r="F5">
-        <v>17.5</v>
+        <v>20.2</v>
       </c>
       <c r="G5">
-        <v>14.4</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>11.6</v>
+        <v>4.9</v>
       </c>
       <c r="I5">
-        <v>8.5</v>
+        <v>2.9</v>
       </c>
       <c r="J5">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="K5">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>71.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>20.6</v>
       </c>
       <c r="E6">
-        <v>19.9</v>
+        <v>23.8</v>
       </c>
       <c r="F6">
         <v>21.8</v>
       </c>
       <c r="G6">
-        <v>14.7</v>
+        <v>15.4</v>
       </c>
       <c r="H6">
-        <v>12.8</v>
+        <v>9.4</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="J6">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>68.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.1</v>
       </c>
-      <c r="C7">
-        <v>1.5</v>
-      </c>
       <c r="D7">
-        <v>17.4</v>
+        <v>3.5</v>
       </c>
       <c r="E7">
-        <v>17.4</v>
+        <v>10.2</v>
       </c>
       <c r="F7">
+        <v>15.2</v>
+      </c>
+      <c r="G7">
+        <v>22.9</v>
+      </c>
+      <c r="H7">
         <v>16.9</v>
       </c>
-      <c r="G7">
-        <v>14.3</v>
-      </c>
-      <c r="H7">
-        <v>11.9</v>
-      </c>
       <c r="I7">
-        <v>8.5</v>
+        <v>15.4</v>
       </c>
       <c r="J7">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
       <c r="K7">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>67.59999999999999</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>0.1</v>
       </c>
       <c r="D8">
-        <v>5.9</v>
+        <v>3.2</v>
       </c>
       <c r="E8">
+        <v>6.4</v>
+      </c>
+      <c r="F8">
         <v>11.2</v>
       </c>
-      <c r="F8">
-        <v>13</v>
-      </c>
       <c r="G8">
-        <v>18.5</v>
+        <v>19.1</v>
       </c>
       <c r="H8">
-        <v>19.5</v>
+        <v>21.1</v>
       </c>
       <c r="I8">
-        <v>16.6</v>
+        <v>18</v>
       </c>
       <c r="J8">
-        <v>10.4</v>
+        <v>13.5</v>
       </c>
       <c r="K8">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
-        <v>48.8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="D9">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="E9">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="F9">
-        <v>10.4</v>
+        <v>6.2</v>
       </c>
       <c r="G9">
-        <v>13</v>
+        <v>11.4</v>
       </c>
       <c r="H9">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="I9">
-        <v>14.1</v>
+        <v>21.4</v>
       </c>
       <c r="J9">
-        <v>15.6</v>
+        <v>20.2</v>
       </c>
       <c r="K9">
-        <v>15.1</v>
+        <v>15.5</v>
       </c>
       <c r="L9">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N9">
-        <v>41.3</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F10">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="G10">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="H10">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="I10">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="J10">
-        <v>25.9</v>
+        <v>22.9</v>
       </c>
       <c r="K10">
-        <v>27.9</v>
+        <v>20.9</v>
       </c>
       <c r="L10">
-        <v>0.7</v>
+        <v>6.2</v>
       </c>
       <c r="M10">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="N10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2183,42 +2276,42 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="E11">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="F11">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="G11">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="H11">
-        <v>12.4</v>
+        <v>9.5</v>
       </c>
       <c r="I11">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="J11">
-        <v>24.5</v>
+        <v>23.6</v>
       </c>
       <c r="K11">
-        <v>33.9</v>
+        <v>30.5</v>
       </c>
       <c r="L11">
-        <v>1.3</v>
+        <v>12.2</v>
       </c>
       <c r="M11">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="N11">
-        <v>11.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2236,33 +2329,33 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J12">
+        <v>5.2</v>
+      </c>
+      <c r="K12">
+        <v>15.6</v>
+      </c>
+      <c r="L12">
+        <v>51.3</v>
+      </c>
+      <c r="M12">
+        <v>25.5</v>
+      </c>
+      <c r="N12">
         <v>0.1</v>
-      </c>
-      <c r="K12">
-        <v>1.2</v>
-      </c>
-      <c r="L12">
-        <v>51.5</v>
-      </c>
-      <c r="M12">
-        <v>47.2</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2283,22 +2376,22 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J13">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="L13">
-        <v>45</v>
+        <v>24.6</v>
       </c>
       <c r="M13">
-        <v>52.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2311,21 +2404,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>38</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2338,158 +2434,194 @@
       <c r="D2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
         <v>99.90000000000001</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="D3">
+      <c r="E3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="C4">
+        <v>47.9</v>
+      </c>
+      <c r="D4">
+        <v>90.3</v>
+      </c>
+      <c r="E4">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>89.60000000000001</v>
+      </c>
+      <c r="D5">
+        <v>88.7</v>
+      </c>
+      <c r="E5">
+        <v>88.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>22.3</v>
+      </c>
+      <c r="C6">
+        <v>71</v>
+      </c>
+      <c r="D6">
+        <v>85.8</v>
+      </c>
+      <c r="E6">
+        <v>82.59999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>37.5</v>
+      </c>
+      <c r="C7">
+        <v>52.3</v>
+      </c>
+      <c r="D7">
+        <v>48.3</v>
+      </c>
+      <c r="E7">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>8.1</v>
+      </c>
+      <c r="C8">
+        <v>14.2</v>
+      </c>
+      <c r="D8">
+        <v>46.7</v>
+      </c>
+      <c r="E8">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>74.2</v>
+      </c>
+      <c r="D9">
+        <v>21.3</v>
+      </c>
+      <c r="E9">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
         <v>99.90000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4">
-        <v>100</v>
-      </c>
-      <c r="C4">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="D4">
-        <v>78.40000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>23</v>
-      </c>
-      <c r="C5">
-        <v>72.2</v>
-      </c>
-      <c r="D5">
-        <v>72.39999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>39.3</v>
-      </c>
-      <c r="C6">
-        <v>57.09999999999999</v>
-      </c>
-      <c r="D6">
-        <v>67.10000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>3.7</v>
-      </c>
-      <c r="C7">
-        <v>67.5</v>
-      </c>
-      <c r="D7">
-        <v>65.40000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="C8">
-        <v>50.8</v>
-      </c>
-      <c r="D8">
-        <v>49.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>99.8</v>
-      </c>
-      <c r="C9">
-        <v>46.1</v>
-      </c>
-      <c r="D9">
-        <v>44.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>8.9</v>
-      </c>
       <c r="C10">
-        <v>14.3</v>
+        <v>37.3</v>
       </c>
       <c r="D10">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>9.700000000000001</v>
+      </c>
+      <c r="E10">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B11">
-        <v>35.3</v>
+        <v>36.5</v>
       </c>
       <c r="C11">
-        <v>13.1</v>
+        <v>13.5</v>
       </c>
       <c r="D11">
-        <v>9.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>8.5</v>
+      </c>
+      <c r="E11">
+        <v>7.399999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>1.8</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0.6</v>
+      </c>
+      <c r="E12">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B12">
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>0.1</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13">
-        <v>1.6</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
       <c r="D13">
+        <v>0.1</v>
+      </c>
+      <c r="E13">
         <v>0</v>
       </c>
     </row>
@@ -2505,28 +2637,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2534,28 +2666,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2">
-        <v>86.98</v>
+        <v>96.17</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>123.3</v>
+        <v>118.89</v>
       </c>
       <c r="G2">
-        <v>0.583</v>
+        <v>0.545</v>
       </c>
       <c r="H2">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2563,28 +2695,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D3">
-        <v>116.37</v>
+        <v>119.33</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>120.4</v>
+        <v>116.79</v>
       </c>
       <c r="G3">
-        <v>0.542</v>
+        <v>0.455</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2592,28 +2724,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4">
-        <v>118.28</v>
+        <v>115.47</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>118.54</v>
+        <v>117.14</v>
       </c>
       <c r="G4">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2621,28 +2753,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5">
+        <v>90.06999999999999</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <v>119.45</v>
+      </c>
+      <c r="G5">
+        <v>0.545</v>
+      </c>
+      <c r="H5">
+        <v>0.5</v>
+      </c>
+      <c r="I5">
         <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5">
-        <v>124.49</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5">
-        <v>117.91</v>
-      </c>
-      <c r="G5">
-        <v>0.458</v>
-      </c>
-      <c r="H5">
-        <v>0.8</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2650,28 +2782,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>85.43000000000001</v>
+        <v>107.69</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
       <c r="F6">
-        <v>119.69</v>
+        <v>117.84</v>
       </c>
       <c r="G6">
-        <v>0.542</v>
+        <v>0.515</v>
       </c>
       <c r="H6">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2679,28 +2811,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7">
-        <v>117.47</v>
+        <v>110.72</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>117.56</v>
+        <v>117.57</v>
       </c>
       <c r="G7">
-        <v>0.417</v>
+        <v>0.545</v>
       </c>
       <c r="H7">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2708,28 +2840,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D8">
-        <v>112.89</v>
+        <v>110.87</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>118.32</v>
+        <v>117.56</v>
       </c>
       <c r="G8">
-        <v>0.583</v>
+        <v>0.485</v>
       </c>
       <c r="H8">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2737,28 +2869,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9">
-        <v>106.49</v>
+        <v>109.84</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>116.18</v>
+        <v>117.65</v>
       </c>
       <c r="G9">
-        <v>0.458</v>
+        <v>0.515</v>
       </c>
       <c r="H9">
-        <v>-0.7</v>
+        <v>0.1</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2766,28 +2898,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D10">
-        <v>124.1</v>
+        <v>124.42</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
       </c>
       <c r="F10">
-        <v>117.97</v>
+        <v>116.32</v>
       </c>
       <c r="G10">
-        <v>0.542</v>
+        <v>0.485</v>
       </c>
       <c r="H10">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2795,28 +2927,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D11">
-        <v>125.49</v>
+        <v>154.02</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>117.34</v>
+        <v>113.63</v>
       </c>
       <c r="G11">
-        <v>0.542</v>
+        <v>0.455</v>
       </c>
       <c r="H11">
         <v>-0.8</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2824,28 +2956,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D12">
-        <v>145.94</v>
+        <v>142.95</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
       <c r="F12">
-        <v>115.47</v>
+        <v>114.64</v>
       </c>
       <c r="G12">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="I12">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2853,28 +2985,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13">
-        <v>151.32</v>
+        <v>122.45</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>112.58</v>
+        <v>116.5</v>
       </c>
       <c r="G13">
-        <v>0.417</v>
+        <v>0.545</v>
       </c>
       <c r="H13">
         <v>-1.3</v>
       </c>
       <c r="I13">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2889,31 +3021,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2921,16 +3053,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>151.32</v>
+        <v>142.9466666666667</v>
       </c>
       <c r="E2">
-        <v>302.64</v>
+        <v>428.84</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2939,10 +3071,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2950,16 +3082,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>145.94</v>
+        <v>154.02</v>
       </c>
       <c r="E3">
-        <v>291.88</v>
+        <v>462.06</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -2968,213 +3100,213 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>124.49</v>
+        <v>124.42</v>
       </c>
       <c r="E4">
-        <v>248.98</v>
+        <v>373.26</v>
       </c>
       <c r="F4">
-        <v>74.90000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>117.47</v>
+        <v>119.3266666666667</v>
       </c>
       <c r="E5">
-        <v>234.94</v>
+        <v>357.98</v>
       </c>
       <c r="F5">
-        <v>71.89999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>125.49</v>
+        <v>115.4666666666667</v>
       </c>
       <c r="E6">
-        <v>250.98</v>
+        <v>346.4</v>
       </c>
       <c r="F6">
-        <v>68.89999999999999</v>
+        <v>84.39999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>124.1</v>
+        <v>122.4466666666667</v>
       </c>
       <c r="E7">
-        <v>248.2</v>
+        <v>367.34</v>
       </c>
       <c r="F7">
-        <v>67.60000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D8">
-        <v>118.28</v>
+        <v>110.8666666666667</v>
       </c>
       <c r="E8">
-        <v>236.56</v>
+        <v>332.6</v>
       </c>
       <c r="F8">
-        <v>48.8</v>
+        <v>40</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>116.37</v>
+        <v>109.84</v>
       </c>
       <c r="E9">
-        <v>232.74</v>
+        <v>329.52</v>
       </c>
       <c r="F9">
-        <v>41.3</v>
+        <v>21.1</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10">
-        <v>106.49</v>
+        <v>107.6933333333333</v>
       </c>
       <c r="E10">
-        <v>212.98</v>
+        <v>323.08</v>
       </c>
       <c r="F10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="G10">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3182,86 +3314,86 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>112.89</v>
+        <v>110.72</v>
       </c>
       <c r="E11">
-        <v>225.78</v>
+        <v>332.16</v>
       </c>
       <c r="F11">
-        <v>11.1</v>
+        <v>6.3</v>
       </c>
       <c r="G11">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="H11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>86.97999999999999</v>
+        <v>96.16666666666667</v>
       </c>
       <c r="E12">
-        <v>173.96</v>
+        <v>288.5</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G12">
-        <v>47.2</v>
+        <v>25.5</v>
       </c>
       <c r="H12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>85.43000000000001</v>
+        <v>90.06666666666666</v>
       </c>
       <c r="E13">
-        <v>170.86</v>
+        <v>270.2</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>52.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3276,19 +3408,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3296,19 +3428,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3316,19 +3448,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3339,16 +3471,16 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3356,10 +3488,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -3368,7 +3500,7 @@
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3376,19 +3508,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3396,19 +3528,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3416,19 +3548,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D8">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3439,16 +3571,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3459,16 +3591,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D10">
         <v>-5</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3479,16 +3611,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3496,19 +3628,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D12">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3519,16 +3651,16 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3538,49 +3670,58 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
       <c r="C3">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3590,67 +3731,82 @@
       <c r="C4">
         <v>7</v>
       </c>
-      <c r="D4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>-2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>7</v>
       </c>
-      <c r="D5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="D6">
+        <v>-1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>4</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="D6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
+      <c r="D7">
         <v>-2</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="C8">
-        <v>-3</v>
-      </c>
-      <c r="D8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>-7</v>
+      </c>
+      <c r="D8">
+        <v>-2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -3660,11 +3816,14 @@
       <c r="C9">
         <v>-4</v>
       </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="D9">
+        <v>-5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -3674,11 +3833,14 @@
       <c r="C10">
         <v>-5</v>
       </c>
-      <c r="D10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="D10">
+        <v>-5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -3688,25 +3850,31 @@
       <c r="C11">
         <v>-5</v>
       </c>
-      <c r="D11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="D11">
+        <v>-7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>-7</v>
-      </c>
-      <c r="D12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>-3</v>
+      </c>
+      <c r="D12">
+        <v>-9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -3716,8 +3884,11 @@
       <c r="C13">
         <v>-15</v>
       </c>
-      <c r="D13" t="s">
-        <v>101</v>
+      <c r="D13">
+        <v>-12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Family Fantasy 2026.xlsx
+++ b/data/leagues/Family Fantasy 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="118">
   <si>
     <t>Noah's Nifty Team</t>
   </si>
@@ -61,19 +61,22 @@
     <t>That movie was great...</t>
   </si>
   <si>
-    <t>3-0-0</t>
-  </si>
-  <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>0-3-0</t>
-  </si>
-  <si>
-    <t>1-1-1</t>
+    <t>4-0-0</t>
+  </si>
+  <si>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>0-4-0</t>
+  </si>
+  <si>
+    <t>1-2-1</t>
   </si>
   <si>
     <t>Teams</t>
@@ -145,6 +148,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -166,42 +172,42 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Gabe Musty</t>
+  </si>
+  <si>
     <t>D Swizzle</t>
   </si>
   <si>
+    <t>lawrence wallach</t>
+  </si>
+  <si>
+    <t>Louis Rodriguez</t>
+  </si>
+  <si>
+    <t>Diana Wallach</t>
+  </si>
+  <si>
     <t>Zach Wallach</t>
   </si>
   <si>
-    <t>Gabe Musty</t>
-  </si>
-  <si>
     <t>Jordan Wallach</t>
   </si>
   <si>
+    <t>Kari Dickert</t>
+  </si>
+  <si>
+    <t>Michael Dickert</t>
+  </si>
+  <si>
     <t>Jackson Jansorn</t>
   </si>
   <si>
-    <t>Michael Dickert</t>
-  </si>
-  <si>
-    <t>lawrence wallach</t>
-  </si>
-  <si>
-    <t>Louis Rodriguez</t>
-  </si>
-  <si>
-    <t>Kari Dickert</t>
+    <t>Noah Wallach</t>
   </si>
   <si>
     <t>Ted Wallach</t>
   </si>
   <si>
-    <t>Noah Wallach</t>
-  </si>
-  <si>
-    <t>Diana Wallach</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -226,58 +232,61 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>11.8-2.1-0.1</t>
-  </si>
-  <si>
-    <t>12.9-1.1-0.1</t>
-  </si>
-  <si>
-    <t>8.6-5.3-0.1</t>
-  </si>
-  <si>
-    <t>8.7-5.2-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.5-0.1</t>
-  </si>
-  <si>
-    <t>6.4-7.5-0.1</t>
-  </si>
-  <si>
-    <t>6.6-7.3-0.1</t>
-  </si>
-  <si>
-    <t>5.7-8.2-0.1</t>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>11.1-2.8-0.1</t>
+  </si>
+  <si>
+    <t>11.5-2.3-0.1</t>
+  </si>
+  <si>
+    <t>9.8-4.1-0.1</t>
+  </si>
+  <si>
+    <t>9.2-4.7-0.1</t>
+  </si>
+  <si>
+    <t>7.4-6.5-0.1</t>
+  </si>
+  <si>
+    <t>5.5-8.3-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.0-0.1</t>
   </si>
   <si>
     <t>5.3-8.6-0.1</t>
   </si>
   <si>
-    <t>4.5-9.4-0.1</t>
-  </si>
-  <si>
-    <t>2.8-11.1-0.1</t>
-  </si>
-  <si>
-    <t>1.8-12.1-0.1</t>
+    <t>4.3-9.6-0.1</t>
+  </si>
+  <si>
+    <t>3.8-10.1-0.1</t>
+  </si>
+  <si>
+    <t>2.3-11.6-0.1</t>
+  </si>
+  <si>
+    <t>11-3</t>
   </si>
   <si>
     <t>12-2</t>
   </si>
   <si>
-    <t>13-1</t>
+    <t>10-4</t>
   </si>
   <si>
     <t>9-5</t>
@@ -286,15 +295,15 @@
     <t>8-6</t>
   </si>
   <si>
-    <t>7-7</t>
-  </si>
-  <si>
     <t>6-8</t>
   </si>
   <si>
     <t>5-9</t>
   </si>
   <si>
+    <t>4-10</t>
+  </si>
+  <si>
     <t>2-12</t>
   </si>
   <si>
@@ -307,42 +316,36 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑4</t>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓5</t>
   </si>
   <si>
     <t>↑1</t>
   </si>
   <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑10</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
     <t>↑2</t>
   </si>
   <si>
-    <t>↑6</t>
-  </si>
-  <si>
-    <t>↓8</t>
-  </si>
-  <si>
-    <t>↓4</t>
-  </si>
-  <si>
-    <t>↑5</t>
-  </si>
-  <si>
-    <t>↓1</t>
+    <t>↓7</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -350,6 +353,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -777,7 +783,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -795,16 +801,16 @@
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M2" t="s">
         <v>12</v>
@@ -818,19 +824,19 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
         <v>13</v>
@@ -839,13 +845,13 @@
         <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
         <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M3" t="s">
         <v>13</v>
@@ -859,34 +865,34 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" t="s">
         <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" t="s">
-        <v>15</v>
       </c>
       <c r="M4" t="s">
         <v>13</v>
@@ -897,37 +903,37 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M5" t="s">
         <v>13</v>
@@ -941,13 +947,13 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -959,16 +965,16 @@
         <v>13</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6" t="s">
         <v>13</v>
       </c>
       <c r="L6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M6" t="s">
         <v>13</v>
@@ -979,13 +985,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -994,7 +1000,7 @@
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -1003,16 +1009,16 @@
         <v>14</v>
       </c>
       <c r="J7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1020,16 +1026,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -1038,19 +1044,19 @@
         <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" t="s">
         <v>13</v>
       </c>
-      <c r="K8" t="s">
-        <v>12</v>
-      </c>
       <c r="L8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M8" t="s">
         <v>12</v>
@@ -1067,22 +1073,22 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J9" t="s">
         <v>14</v>
@@ -1091,10 +1097,10 @@
         <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1105,7 +1111,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1117,16 +1123,16 @@
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K10" t="s">
         <v>14</v>
@@ -1143,37 +1149,37 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
         <v>13</v>
       </c>
       <c r="J11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M11" t="s">
         <v>12</v>
@@ -1184,40 +1190,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" t="s">
         <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" t="s">
-        <v>13</v>
-      </c>
-      <c r="L12" t="s">
-        <v>15</v>
-      </c>
-      <c r="M12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1231,10 +1237,10 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
@@ -1246,7 +1252,7 @@
         <v>13</v>
       </c>
       <c r="I13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J13" t="s">
         <v>14</v>
@@ -1255,7 +1261,7 @@
         <v>14</v>
       </c>
       <c r="L13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M13" t="s">
         <v>12</v>
@@ -1268,30 +1274,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1299,25 +1305,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="F2">
-        <v>-7</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1325,25 +1331,25 @@
         <v>1</v>
       </c>
       <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
       <c r="E3">
-        <v>-9</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1351,25 +1357,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>-7</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1380,22 +1386,100 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>-9</v>
+      </c>
+      <c r="F5">
+        <v>-1</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
         <v>1</v>
       </c>
-      <c r="E5">
+      <c r="E7">
         <v>-7</v>
       </c>
-      <c r="F5">
+      <c r="F7">
         <v>-2</v>
       </c>
-      <c r="G5">
+      <c r="G7">
         <v>5</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H7" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1494,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1427,10 +1511,10 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1438,13 +1522,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.8333333333333334</v>
+        <v>1.25</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1452,13 +1536,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1.166666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1466,13 +1550,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>1.25</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1483,10 +1567,10 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>1.416666666666667</v>
+        <v>1.75</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1494,13 +1578,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>1.416666666666667</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1508,13 +1592,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>1.583333333333333</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1522,13 +1606,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>1.666666666666667</v>
+        <v>2.25</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1536,13 +1620,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>1.666666666666667</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1553,10 +1637,10 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>1.916666666666667</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1567,7 +1651,7 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>2.166666666666667</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
@@ -1581,7 +1665,7 @@
         <v>11</v>
       </c>
       <c r="C13">
-        <v>2.333333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
@@ -1599,16 +1683,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1619,10 +1703,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2.75</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D2">
-        <v>-0.25</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1636,13 +1720,13 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>2.666666666666667</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D3">
-        <v>-0.3333333333333335</v>
+        <v>-0.08333333333333348</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1650,16 +1734,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1667,13 +1751,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>1.666666666666667</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="D5">
-        <v>1.666666666666667</v>
+        <v>0.4166666666666665</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -1684,13 +1768,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>1.583333333333333</v>
+        <v>2.25</v>
       </c>
       <c r="D6">
-        <v>-1.416666666666667</v>
+        <v>-1.75</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -1701,16 +1785,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>1.583333333333333</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>-1.416666666666667</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1718,16 +1802,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1.416666666666667</v>
+        <v>1.75</v>
       </c>
       <c r="D8">
-        <v>-0.5833333333333333</v>
+        <v>1.75</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1735,16 +1819,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>1.166666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D9">
-        <v>0.1666666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1752,16 +1836,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1769,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -1786,16 +1870,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>0.6666666666666666</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D12">
-        <v>0.6666666666666666</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1803,16 +1887,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>0.4166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D13">
-        <v>0.4166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1827,72 +1911,72 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>20.4</v>
+        <v>38.9</v>
       </c>
       <c r="C2">
-        <v>70.3</v>
+        <v>40.4</v>
       </c>
       <c r="D2">
-        <v>7.3</v>
+        <v>14.7</v>
       </c>
       <c r="E2">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="F2">
+        <v>1.8</v>
+      </c>
+      <c r="G2">
         <v>0.1</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1910,36 +1994,36 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B3">
-        <v>79</v>
+        <v>49.5</v>
       </c>
       <c r="C3">
-        <v>19.9</v>
+        <v>32.9</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>12.6</v>
       </c>
       <c r="E3">
+        <v>3.4</v>
+      </c>
+      <c r="F3">
+        <v>1.3</v>
+      </c>
+      <c r="G3">
         <v>0.1</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1954,43 +2038,43 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>15.6</v>
+      </c>
+      <c r="D4">
+        <v>35.1</v>
+      </c>
+      <c r="E4">
+        <v>24.5</v>
+      </c>
+      <c r="F4">
+        <v>10.1</v>
+      </c>
+      <c r="G4">
+        <v>5.5</v>
+      </c>
+      <c r="H4">
+        <v>1.1</v>
+      </c>
+      <c r="I4">
+        <v>0.8</v>
+      </c>
+      <c r="J4">
+        <v>0.2</v>
+      </c>
+      <c r="K4">
         <v>0.1</v>
       </c>
-      <c r="C4">
-        <v>3.9</v>
-      </c>
-      <c r="D4">
-        <v>31.4</v>
-      </c>
-      <c r="E4">
-        <v>27.8</v>
-      </c>
-      <c r="F4">
-        <v>18.8</v>
-      </c>
-      <c r="G4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H4">
-        <v>5.1</v>
-      </c>
-      <c r="I4">
-        <v>2.9</v>
-      </c>
-      <c r="J4">
-        <v>0.9</v>
-      </c>
-      <c r="K4">
-        <v>0.3</v>
-      </c>
       <c r="L4">
         <v>0</v>
       </c>
@@ -1998,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>90.8</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -2006,175 +2090,175 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>2.9</v>
+        <v>8.5</v>
       </c>
       <c r="D5">
-        <v>31.7</v>
+        <v>23.7</v>
       </c>
       <c r="E5">
-        <v>24.2</v>
+        <v>30.2</v>
       </c>
       <c r="F5">
-        <v>20.2</v>
+        <v>16.4</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H5">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="I5">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J5">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>90.40000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>0.1</v>
       </c>
       <c r="C6">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="D6">
-        <v>20.6</v>
+        <v>6.5</v>
       </c>
       <c r="E6">
-        <v>23.8</v>
+        <v>16.9</v>
       </c>
       <c r="F6">
-        <v>21.8</v>
+        <v>24.6</v>
       </c>
       <c r="G6">
-        <v>15.4</v>
+        <v>22.4</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="I6">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="J6">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="K6">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="L6">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>84.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="D7">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="E7">
-        <v>10.2</v>
+        <v>14.6</v>
       </c>
       <c r="F7">
-        <v>15.2</v>
+        <v>25.7</v>
       </c>
       <c r="G7">
-        <v>22.9</v>
+        <v>21.7</v>
       </c>
       <c r="H7">
-        <v>16.9</v>
+        <v>13.6</v>
       </c>
       <c r="I7">
-        <v>15.4</v>
+        <v>8.4</v>
       </c>
       <c r="J7">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="K7">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="L7">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>51.9</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="E8">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="F8">
-        <v>11.2</v>
+        <v>8.1</v>
       </c>
       <c r="G8">
-        <v>19.1</v>
+        <v>14.7</v>
       </c>
       <c r="H8">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="I8">
-        <v>18</v>
+        <v>19.7</v>
       </c>
       <c r="J8">
-        <v>13.5</v>
+        <v>17.4</v>
       </c>
       <c r="K8">
-        <v>6.4</v>
+        <v>10.6</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="N8">
-        <v>40</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2182,48 +2266,48 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E9">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>11.4</v>
+        <v>13.1</v>
       </c>
       <c r="H9">
-        <v>18</v>
+        <v>20.5</v>
       </c>
       <c r="I9">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="J9">
-        <v>20.2</v>
+        <v>17.2</v>
       </c>
       <c r="K9">
-        <v>15.5</v>
+        <v>10.8</v>
       </c>
       <c r="L9">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="M9">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="N9">
-        <v>21.1</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2232,42 +2316,42 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E10">
+        <v>0.9</v>
+      </c>
+      <c r="F10">
         <v>2.5</v>
       </c>
-      <c r="F10">
-        <v>4.7</v>
-      </c>
       <c r="G10">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H10">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="I10">
-        <v>18.8</v>
+        <v>17.9</v>
       </c>
       <c r="J10">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="K10">
-        <v>20.9</v>
+        <v>19.3</v>
       </c>
       <c r="L10">
-        <v>6.2</v>
+        <v>11.1</v>
       </c>
       <c r="M10">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="N10">
-        <v>15</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2279,39 +2363,39 @@
         <v>0.1</v>
       </c>
       <c r="E11">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F11">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="G11">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H11">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>15.6</v>
+        <v>14.7</v>
       </c>
       <c r="J11">
-        <v>23.6</v>
+        <v>18.6</v>
       </c>
       <c r="K11">
-        <v>30.5</v>
+        <v>23.4</v>
       </c>
       <c r="L11">
-        <v>12.2</v>
+        <v>21.5</v>
       </c>
       <c r="M11">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="N11">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2323,39 +2407,39 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G12">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="I12">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J12">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="K12">
-        <v>15.6</v>
+        <v>24.1</v>
       </c>
       <c r="L12">
-        <v>51.3</v>
+        <v>35.7</v>
       </c>
       <c r="M12">
-        <v>25.5</v>
+        <v>19.1</v>
       </c>
       <c r="N12">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2373,28 +2457,28 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H13">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="I13">
+        <v>0.4</v>
+      </c>
+      <c r="J13">
+        <v>2.3</v>
+      </c>
+      <c r="K13">
+        <v>7.2</v>
+      </c>
+      <c r="L13">
+        <v>21</v>
+      </c>
+      <c r="M13">
+        <v>68.3</v>
+      </c>
+      <c r="N13">
         <v>0.2</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>4.5</v>
-      </c>
-      <c r="L13">
-        <v>24.6</v>
-      </c>
-      <c r="M13">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2404,24 +2488,27 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2432,18 +2519,21 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="C3">
         <v>99.90000000000001</v>
@@ -2452,27 +2542,33 @@
         <v>100</v>
       </c>
       <c r="E3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="F3">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>90.90000000000001</v>
+        <v>20.6</v>
       </c>
       <c r="C4">
-        <v>47.9</v>
+        <v>71.39999999999999</v>
       </c>
       <c r="D4">
-        <v>90.3</v>
+        <v>83.3</v>
       </c>
       <c r="E4">
-        <v>92.90000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="F4">
+        <v>96.09999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -2480,149 +2576,176 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>89.60000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="D5">
-        <v>88.7</v>
+        <v>90.2</v>
       </c>
       <c r="E5">
-        <v>88.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>94.39999999999999</v>
+      </c>
+      <c r="F5">
+        <v>94.89999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>22.3</v>
+        <v>90.7</v>
       </c>
       <c r="C6">
-        <v>71</v>
+        <v>47.5</v>
       </c>
       <c r="D6">
-        <v>85.8</v>
+        <v>91</v>
       </c>
       <c r="E6">
-        <v>82.59999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F6">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>37.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C7">
-        <v>52.3</v>
+        <v>37.6</v>
       </c>
       <c r="D7">
-        <v>48.3</v>
+        <v>9.6</v>
       </c>
       <c r="E7">
-        <v>50.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>66.5</v>
+      </c>
+      <c r="F7">
+        <v>70.39999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8">
-        <v>8.1</v>
+        <v>41.5</v>
       </c>
       <c r="C8">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="D8">
-        <v>46.7</v>
+        <v>7.5</v>
       </c>
       <c r="E8">
-        <v>39.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>26.9</v>
+      </c>
+      <c r="F8">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B9">
+        <v>2.2</v>
+      </c>
+      <c r="C9">
+        <v>72.5</v>
+      </c>
+      <c r="D9">
+        <v>22.6</v>
+      </c>
+      <c r="E9">
+        <v>22.2</v>
+      </c>
+      <c r="F9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>9.1</v>
+      </c>
+      <c r="C10">
+        <v>15.5</v>
+      </c>
+      <c r="D10">
+        <v>47</v>
+      </c>
+      <c r="E10">
+        <v>11.7</v>
+      </c>
+      <c r="F10">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>35.4</v>
+      </c>
+      <c r="C11">
+        <v>53.40000000000001</v>
+      </c>
+      <c r="D11">
+        <v>48.6</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C9">
-        <v>74.2</v>
-      </c>
-      <c r="D9">
-        <v>21.3</v>
-      </c>
-      <c r="E9">
-        <v>22.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="C10">
-        <v>37.3</v>
-      </c>
-      <c r="D10">
-        <v>9.700000000000001</v>
-      </c>
-      <c r="E10">
-        <v>14.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11">
-        <v>36.5</v>
-      </c>
-      <c r="C11">
-        <v>13.5</v>
-      </c>
-      <c r="D11">
-        <v>8.5</v>
-      </c>
-      <c r="E11">
-        <v>7.399999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
+      <c r="B12">
+        <v>0.2</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0.8</v>
+      </c>
+      <c r="F12">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B12">
-        <v>1.8</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
+      <c r="B13">
         <v>0.6</v>
       </c>
-      <c r="E12">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
       <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0.3</v>
+      </c>
+      <c r="E13">
         <v>0.1</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>0.1</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2637,28 +2760,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2666,28 +2789,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>96.17</v>
+        <v>126.04</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>118.89</v>
+        <v>119.57</v>
       </c>
       <c r="G2">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2695,28 +2818,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>119.33</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>116.79</v>
+        <v>119.57</v>
       </c>
       <c r="G3">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2724,28 +2847,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D4">
-        <v>115.47</v>
+        <v>106.38</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>117.14</v>
+        <v>120.11</v>
       </c>
       <c r="G4">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="H4">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2753,28 +2876,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5">
-        <v>90.06999999999999</v>
+        <v>110.25</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
       </c>
       <c r="F5">
-        <v>119.45</v>
+        <v>120.11</v>
       </c>
       <c r="G5">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="H5">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2782,28 +2905,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6">
-        <v>107.69</v>
+        <v>112.22</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>117.84</v>
+        <v>118.46</v>
       </c>
       <c r="G6">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="H6">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2811,28 +2934,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D7">
-        <v>110.72</v>
+        <v>120.86</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>117.57</v>
+        <v>118.46</v>
       </c>
       <c r="G7">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="H7">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2840,28 +2963,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D8">
-        <v>110.87</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>117.56</v>
+        <v>119.51</v>
       </c>
       <c r="G8">
-        <v>0.485</v>
+        <v>0.525</v>
       </c>
       <c r="H8">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2869,28 +2992,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D9">
-        <v>109.84</v>
+        <v>122.78</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>117.65</v>
+        <v>119.51</v>
       </c>
       <c r="G9">
-        <v>0.515</v>
+        <v>0.525</v>
       </c>
       <c r="H9">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2898,28 +3021,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>124.42</v>
+        <v>122.28</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F10">
-        <v>116.32</v>
+        <v>117.43</v>
       </c>
       <c r="G10">
-        <v>0.485</v>
+        <v>0.55</v>
       </c>
       <c r="H10">
-        <v>-0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2927,28 +3050,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D11">
-        <v>154.02</v>
+        <v>121.17</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>113.63</v>
+        <v>117.43</v>
       </c>
       <c r="G11">
-        <v>0.455</v>
+        <v>0.55</v>
       </c>
       <c r="H11">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2959,25 +3082,25 @@
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D12">
-        <v>142.95</v>
+        <v>136.69</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
       <c r="F12">
-        <v>114.64</v>
+        <v>113.78</v>
       </c>
       <c r="G12">
-        <v>0.455</v>
+        <v>0.425</v>
       </c>
       <c r="H12">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2985,28 +3108,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13">
+        <v>143.25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13">
+        <v>113.78</v>
+      </c>
+      <c r="G13">
+        <v>0.425</v>
+      </c>
+      <c r="H13">
+        <v>-1.8</v>
+      </c>
+      <c r="I13">
         <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13">
-        <v>122.45</v>
-      </c>
-      <c r="E13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13">
-        <v>116.5</v>
-      </c>
-      <c r="G13">
-        <v>0.545</v>
-      </c>
-      <c r="H13">
-        <v>-1.3</v>
-      </c>
-      <c r="I13">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3021,118 +3144,118 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D2">
-        <v>142.9466666666667</v>
+        <v>143.245</v>
       </c>
       <c r="E2">
-        <v>428.84</v>
+        <v>572.98</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>154.02</v>
+        <v>136.685</v>
       </c>
       <c r="E3">
-        <v>462.06</v>
+        <v>546.74</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>124.42</v>
+        <v>126.04</v>
       </c>
       <c r="E4">
-        <v>373.26</v>
+        <v>504.16</v>
       </c>
       <c r="F4">
-        <v>90.8</v>
+        <v>97.8</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3140,115 +3263,115 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>119.3266666666667</v>
+        <v>120.855</v>
       </c>
       <c r="E5">
-        <v>357.98</v>
+        <v>483.42</v>
       </c>
       <c r="F5">
-        <v>90.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>115.4666666666667</v>
+        <v>122.775</v>
       </c>
       <c r="E6">
-        <v>346.4</v>
+        <v>491.1</v>
       </c>
       <c r="F6">
-        <v>84.39999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>122.4466666666667</v>
+        <v>121.165</v>
       </c>
       <c r="E7">
-        <v>367.34</v>
+        <v>484.6600000000001</v>
       </c>
       <c r="F7">
-        <v>51.9</v>
+        <v>69.8</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C8">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>110.8666666666667</v>
+        <v>122.285</v>
       </c>
       <c r="E8">
-        <v>332.6</v>
+        <v>489.14</v>
       </c>
       <c r="F8">
-        <v>40</v>
+        <v>26.1</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3256,144 +3379,144 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>109.84</v>
+        <v>110.25</v>
       </c>
       <c r="E9">
-        <v>329.52</v>
+        <v>441</v>
       </c>
       <c r="F9">
-        <v>21.1</v>
+        <v>22.9</v>
       </c>
       <c r="G9">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>107.6933333333333</v>
+        <v>106.38</v>
       </c>
       <c r="E10">
-        <v>323.08</v>
+        <v>425.52</v>
       </c>
       <c r="F10">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="G10">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>110.72</v>
+        <v>112.215</v>
       </c>
       <c r="E11">
-        <v>332.16</v>
+        <v>448.86</v>
       </c>
       <c r="F11">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="G11">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="H11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D12">
-        <v>96.16666666666667</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="E12">
-        <v>288.5</v>
+        <v>399.28</v>
       </c>
       <c r="F12">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="G12">
-        <v>25.5</v>
+        <v>19.1</v>
       </c>
       <c r="H12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>90.06666666666666</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="E13">
-        <v>270.2</v>
+        <v>383.96</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G13">
-        <v>69.59999999999999</v>
+        <v>68.30000000000001</v>
       </c>
       <c r="H13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3408,19 +3531,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3428,19 +3551,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3448,19 +3571,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3468,19 +3591,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>56</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3488,19 +3611,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3508,19 +3631,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3528,19 +3651,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D7">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3548,19 +3671,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D8">
         <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3568,19 +3691,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9">
         <v>-5</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3588,19 +3711,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3608,19 +3731,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3631,16 +3754,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D12">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3651,16 +3774,16 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D13">
         <v>-12</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -3670,194 +3793,227 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>110</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D2">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>-2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>7</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
         <v>-2</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>-2</v>
+      </c>
+      <c r="C7">
+        <v>-5</v>
+      </c>
+      <c r="D7">
+        <v>-5</v>
+      </c>
+      <c r="E7">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>-1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7">
+      <c r="F7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>-4</v>
+      </c>
+      <c r="C8">
+        <v>-4</v>
+      </c>
+      <c r="D8">
+        <v>-5</v>
+      </c>
+      <c r="E8">
+        <v>-2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>-2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>-6</v>
-      </c>
-      <c r="C8">
-        <v>-7</v>
-      </c>
-      <c r="D8">
-        <v>-2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="B9">
         <v>-4</v>
       </c>
       <c r="C9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D9">
+        <v>-7</v>
+      </c>
+      <c r="E9">
         <v>-5</v>
       </c>
-      <c r="E9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>-1</v>
+      </c>
+      <c r="E10">
+        <v>-6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>-6</v>
+      </c>
+      <c r="C11">
+        <v>-7</v>
+      </c>
+      <c r="D11">
         <v>-2</v>
       </c>
-      <c r="C10">
-        <v>-5</v>
-      </c>
-      <c r="D10">
-        <v>-5</v>
-      </c>
-      <c r="E10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>-4</v>
-      </c>
-      <c r="C11">
-        <v>-5</v>
-      </c>
-      <c r="D11">
-        <v>-7</v>
-      </c>
-      <c r="E11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="E11">
+        <v>-9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -3870,11 +4026,14 @@
       <c r="D12">
         <v>-9</v>
       </c>
-      <c r="E12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="E12">
+        <v>-12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -3887,8 +4046,11 @@
       <c r="D13">
         <v>-12</v>
       </c>
-      <c r="E13" t="s">
-        <v>105</v>
+      <c r="E13">
+        <v>-12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Family Fantasy 2026.xlsx
+++ b/data/leagues/Family Fantasy 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="120">
   <si>
     <t>Noah's Nifty Team</t>
   </si>
@@ -61,22 +61,25 @@
     <t>That movie was great...</t>
   </si>
   <si>
-    <t>4-0-0</t>
-  </si>
-  <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>0-4-0</t>
-  </si>
-  <si>
-    <t>1-2-1</t>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>1-4-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>0-5-0</t>
+  </si>
+  <si>
+    <t>1-3-1</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -151,6 +154,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -172,33 +178,33 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Diana Wallach</t>
+  </si>
+  <si>
+    <t>lawrence wallach</t>
+  </si>
+  <si>
+    <t>Louis Rodriguez</t>
+  </si>
+  <si>
     <t>Gabe Musty</t>
   </si>
   <si>
+    <t>Zach Wallach</t>
+  </si>
+  <si>
     <t>D Swizzle</t>
   </si>
   <si>
-    <t>lawrence wallach</t>
-  </si>
-  <si>
-    <t>Louis Rodriguez</t>
-  </si>
-  <si>
-    <t>Diana Wallach</t>
-  </si>
-  <si>
-    <t>Zach Wallach</t>
-  </si>
-  <si>
     <t>Jordan Wallach</t>
   </si>
   <si>
+    <t>Michael Dickert</t>
+  </si>
+  <si>
     <t>Kari Dickert</t>
   </si>
   <si>
-    <t>Michael Dickert</t>
-  </si>
-  <si>
     <t>Jackson Jansorn</t>
   </si>
   <si>
@@ -232,79 +238,79 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>11.1-2.8-0.1</t>
-  </si>
-  <si>
-    <t>11.5-2.3-0.1</t>
-  </si>
-  <si>
-    <t>9.8-4.1-0.1</t>
-  </si>
-  <si>
-    <t>9.2-4.7-0.1</t>
-  </si>
-  <si>
-    <t>7.4-6.5-0.1</t>
-  </si>
-  <si>
-    <t>5.5-8.3-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.0-0.1</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>5-0</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>11.6-2.4-0.1</t>
+  </si>
+  <si>
+    <t>10.6-3.4-0.1</t>
+  </si>
+  <si>
+    <t>10.6-3.3-0.1</t>
+  </si>
+  <si>
+    <t>8.2-5.7-0.1</t>
+  </si>
+  <si>
+    <t>6.9-7.0-0.1</t>
+  </si>
+  <si>
+    <t>5.4-8.5-0.1</t>
   </si>
   <si>
     <t>5.3-8.6-0.1</t>
   </si>
   <si>
-    <t>4.3-9.6-0.1</t>
-  </si>
-  <si>
-    <t>3.8-10.1-0.1</t>
-  </si>
-  <si>
-    <t>2.3-11.6-0.1</t>
+    <t>4.2-9.7-0.1</t>
+  </si>
+  <si>
+    <t>4.1-9.8-0.1</t>
+  </si>
+  <si>
+    <t>2.9-11.0-0.1</t>
+  </si>
+  <si>
+    <t>12-2</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
-    <t>12-2</t>
-  </si>
-  <si>
-    <t>10-4</t>
-  </si>
-  <si>
     <t>9-5</t>
   </si>
   <si>
     <t>8-6</t>
   </si>
   <si>
+    <t>7-7</t>
+  </si>
+  <si>
+    <t>5-9</t>
+  </si>
+  <si>
     <t>6-8</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
     <t>4-10</t>
   </si>
   <si>
-    <t>2-12</t>
+    <t>3-11</t>
   </si>
   <si>
     <t>Owners</t>
@@ -316,36 +322,33 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
     <t>↓1</t>
   </si>
   <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↑10</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
     <t>↑2</t>
   </si>
   <si>
-    <t>↓7</t>
+    <t>↓11</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
+    <t>↓9</t>
+  </si>
+  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -356,6 +359,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -786,22 +792,22 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -810,7 +816,7 @@
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M2" t="s">
         <v>12</v>
@@ -827,7 +833,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -851,7 +857,7 @@
         <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M3" t="s">
         <v>13</v>
@@ -868,7 +874,7 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -892,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M4" t="s">
         <v>13</v>
@@ -903,40 +909,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" t="s">
         <v>14</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -944,40 +950,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -991,7 +997,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -1006,16 +1012,16 @@
         <v>14</v>
       </c>
       <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" t="s">
         <v>14</v>
-      </c>
-      <c r="J7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" t="s">
-        <v>16</v>
       </c>
       <c r="M7" t="s">
         <v>15</v>
@@ -1026,40 +1032,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M8" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1067,40 +1073,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>14</v>
       </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
       <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
         <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" t="s">
-        <v>16</v>
       </c>
       <c r="J9" t="s">
         <v>14</v>
       </c>
       <c r="K9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
-        <v>16</v>
-      </c>
       <c r="M9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1114,13 +1120,13 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -1129,7 +1135,7 @@
         <v>13</v>
       </c>
       <c r="I10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" t="s">
         <v>15</v>
@@ -1138,7 +1144,7 @@
         <v>14</v>
       </c>
       <c r="L10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M10" t="s">
         <v>12</v>
@@ -1149,37 +1155,37 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M11" t="s">
         <v>12</v>
@@ -1237,13 +1243,13 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -1252,7 +1258,7 @@
         <v>13</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J13" t="s">
         <v>14</v>
@@ -1261,7 +1267,7 @@
         <v>14</v>
       </c>
       <c r="L13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M13" t="s">
         <v>12</v>
@@ -1274,30 +1280,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1331,25 +1337,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>-18</v>
       </c>
       <c r="F3">
         <v>-2</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1357,25 +1363,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1383,25 +1389,25 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
       <c r="E5">
-        <v>-9</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1409,25 +1415,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>-7</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1438,22 +1444,22 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="F7">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1461,24 +1467,102 @@
         <v>6</v>
       </c>
       <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>-7</v>
+      </c>
+      <c r="F9">
+        <v>-2</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
         <v>9</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E10">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
         <v>1</v>
       </c>
-      <c r="E8">
+      <c r="E11">
         <v>5</v>
       </c>
-      <c r="F8">
+      <c r="F11">
         <v>6</v>
       </c>
-      <c r="G8">
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H11" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1494,13 +1578,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1508,10 +1592,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0.9166666666666666</v>
+        <v>1.5</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -1522,13 +1606,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>1.25</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1536,13 +1620,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>1.333333333333333</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1550,10 +1634,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>1.583333333333333</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -1564,13 +1648,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1578,13 +1662,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>1.833333333333333</v>
+        <v>2.25</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1592,13 +1676,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>2.083333333333333</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1606,13 +1690,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1620,10 +1704,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>2.333333333333333</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1634,10 +1718,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>2.416666666666667</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1651,10 +1735,10 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>2.916666666666667</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1665,7 +1749,7 @@
         <v>11</v>
       </c>
       <c r="C13">
-        <v>3.25</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
@@ -1683,16 +1767,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1700,13 +1784,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>3.333333333333333</v>
+        <v>3.916666666666667</v>
       </c>
       <c r="D2">
-        <v>-0.6666666666666665</v>
+        <v>-0.08333333333333348</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1717,16 +1801,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>2.916666666666667</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="D3">
-        <v>-0.08333333333333348</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1737,13 +1821,13 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>2.5</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="D4">
-        <v>-1.5</v>
+        <v>-1.583333333333333</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1754,10 +1838,10 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>2.416666666666667</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="D5">
-        <v>0.4166666666666665</v>
+        <v>0.8333333333333335</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -1768,16 +1852,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>2.25</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D6">
-        <v>-1.75</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1785,16 +1869,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-1.416666666666667</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1802,16 +1886,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>1.75</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="D8">
-        <v>1.75</v>
+        <v>-0.08333333333333326</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1819,13 +1903,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>1.666666666666667</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="D9">
-        <v>1.666666666666667</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
@@ -1839,10 +1923,10 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>1.583333333333333</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D10">
-        <v>-0.4166666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -1856,13 +1940,13 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>1.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D11">
-        <v>-0.5</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1870,13 +1954,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>1.166666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D12">
-        <v>0.1666666666666667</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -1887,13 +1971,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>0.8333333333333334</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D13">
-        <v>0.8333333333333334</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
@@ -1911,46 +1995,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1958,25 +2042,25 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>38.9</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="C2">
-        <v>40.4</v>
+        <v>23.6</v>
       </c>
       <c r="D2">
-        <v>14.7</v>
+        <v>8.6</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="F2">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1994,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -2002,28 +2086,28 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>49.5</v>
+        <v>14.8</v>
       </c>
       <c r="C3">
-        <v>32.9</v>
+        <v>34.6</v>
       </c>
       <c r="D3">
-        <v>12.6</v>
+        <v>37.1</v>
       </c>
       <c r="E3">
-        <v>3.4</v>
+        <v>10.2</v>
       </c>
       <c r="F3">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="H3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2046,34 +2130,34 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>17.6</v>
       </c>
       <c r="C4">
-        <v>15.6</v>
+        <v>33.9</v>
       </c>
       <c r="D4">
-        <v>35.1</v>
+        <v>32.1</v>
       </c>
       <c r="E4">
-        <v>24.5</v>
+        <v>11.3</v>
       </c>
       <c r="F4">
-        <v>10.1</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="H4">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="I4">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2082,144 +2166,144 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>97.8</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="C5">
-        <v>8.5</v>
+        <v>3.7</v>
       </c>
       <c r="D5">
-        <v>23.7</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>30.2</v>
+        <v>34.8</v>
       </c>
       <c r="F5">
-        <v>16.4</v>
+        <v>24.2</v>
       </c>
       <c r="G5">
-        <v>9.699999999999999</v>
+        <v>15.1</v>
       </c>
       <c r="H5">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="I5">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K5">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N5">
-        <v>92.7</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6">
+        <v>0.7</v>
+      </c>
+      <c r="C6">
+        <v>3.7</v>
+      </c>
+      <c r="D6">
+        <v>7.3</v>
+      </c>
+      <c r="E6">
+        <v>25.4</v>
+      </c>
+      <c r="F6">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>16.2</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
+      </c>
+      <c r="I6">
+        <v>3.7</v>
+      </c>
+      <c r="J6">
+        <v>1.6</v>
+      </c>
+      <c r="K6">
         <v>0.1</v>
       </c>
-      <c r="C6">
-        <v>1.1</v>
-      </c>
-      <c r="D6">
-        <v>6.5</v>
-      </c>
-      <c r="E6">
-        <v>16.9</v>
-      </c>
-      <c r="F6">
-        <v>24.6</v>
-      </c>
-      <c r="G6">
-        <v>22.4</v>
-      </c>
-      <c r="H6">
-        <v>14.3</v>
-      </c>
-      <c r="I6">
-        <v>7.8</v>
-      </c>
-      <c r="J6">
-        <v>4.2</v>
-      </c>
-      <c r="K6">
-        <v>1.8</v>
-      </c>
       <c r="L6">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>71.59999999999999</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="E7">
-        <v>14.6</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>25.7</v>
+        <v>22.7</v>
       </c>
       <c r="G7">
-        <v>21.7</v>
+        <v>28.7</v>
       </c>
       <c r="H7">
-        <v>13.6</v>
+        <v>16</v>
       </c>
       <c r="I7">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J7">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="K7">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="L7">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N7">
-        <v>69.8</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2228,86 +2312,86 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="F8">
-        <v>8.1</v>
+        <v>3.6</v>
       </c>
       <c r="G8">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="H8">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="I8">
-        <v>19.7</v>
+        <v>17.9</v>
       </c>
       <c r="J8">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="K8">
-        <v>10.6</v>
+        <v>14.2</v>
       </c>
       <c r="L8">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="M8">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="N8">
-        <v>26.1</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="G9">
-        <v>13.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H9">
-        <v>20.5</v>
+        <v>14.2</v>
       </c>
       <c r="I9">
-        <v>21.8</v>
+        <v>20.3</v>
       </c>
       <c r="J9">
-        <v>17.2</v>
+        <v>18.5</v>
       </c>
       <c r="K9">
-        <v>10.8</v>
+        <v>16.3</v>
       </c>
       <c r="L9">
-        <v>5.6</v>
+        <v>12.6</v>
       </c>
       <c r="M9">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="N9">
-        <v>22.9</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2316,42 +2400,42 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E10">
         <v>0.9</v>
       </c>
       <c r="F10">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="G10">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H10">
-        <v>14.2</v>
+        <v>17.3</v>
       </c>
       <c r="I10">
-        <v>17.9</v>
+        <v>19.5</v>
       </c>
       <c r="J10">
-        <v>23.5</v>
+        <v>17.2</v>
       </c>
       <c r="K10">
-        <v>19.3</v>
+        <v>15.3</v>
       </c>
       <c r="L10">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="M10">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>11.6</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2360,86 +2444,86 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="G11">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="H11">
-        <v>8</v>
+        <v>10.9</v>
       </c>
       <c r="I11">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="J11">
-        <v>18.6</v>
+        <v>17</v>
       </c>
       <c r="K11">
-        <v>23.4</v>
+        <v>19.8</v>
       </c>
       <c r="L11">
-        <v>21.5</v>
+        <v>19.3</v>
       </c>
       <c r="M11">
-        <v>7.6</v>
+        <v>11.8</v>
       </c>
       <c r="N11">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0.1</v>
+      </c>
+      <c r="F12">
+        <v>0.6</v>
+      </c>
+      <c r="G12">
         <v>3</v>
       </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0.3</v>
-      </c>
-      <c r="F12">
-        <v>0.3</v>
-      </c>
-      <c r="G12">
-        <v>0.8</v>
-      </c>
       <c r="H12">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="I12">
-        <v>6.3</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>10.5</v>
+        <v>14.4</v>
       </c>
       <c r="K12">
+        <v>19.3</v>
+      </c>
+      <c r="L12">
         <v>24.1</v>
       </c>
-      <c r="L12">
-        <v>35.7</v>
-      </c>
       <c r="M12">
-        <v>19.1</v>
+        <v>22.7</v>
       </c>
       <c r="N12">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2451,34 +2535,34 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G13">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="H13">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J13">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="K13">
-        <v>7.2</v>
+        <v>12.3</v>
       </c>
       <c r="L13">
-        <v>21</v>
+        <v>22.5</v>
       </c>
       <c r="M13">
-        <v>68.3</v>
+        <v>50.8</v>
       </c>
       <c r="N13">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -2488,55 +2572,61 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>42</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
         <v>99.90000000000001</v>
-      </c>
-      <c r="E2">
-        <v>100</v>
       </c>
       <c r="F2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B3">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -2547,205 +2637,238 @@
       <c r="F3">
         <v>99.90000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>20.6</v>
+        <v>23.2</v>
       </c>
       <c r="C4">
         <v>71.39999999999999</v>
       </c>
       <c r="D4">
-        <v>83.3</v>
+        <v>83.89999999999999</v>
       </c>
       <c r="E4">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="F4">
-        <v>96.09999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G4">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>100</v>
       </c>
       <c r="C5">
+        <v>36.6</v>
+      </c>
+      <c r="D5">
+        <v>11.8</v>
+      </c>
+      <c r="E5">
+        <v>67.10000000000001</v>
+      </c>
+      <c r="F5">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="G5">
         <v>88.3</v>
       </c>
-      <c r="D5">
-        <v>90.2</v>
-      </c>
-      <c r="E5">
-        <v>94.39999999999999</v>
-      </c>
-      <c r="F5">
-        <v>94.89999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>89.60000000000001</v>
+      </c>
+      <c r="D6">
+        <v>89.8</v>
+      </c>
+      <c r="E6">
+        <v>92.30000000000001</v>
+      </c>
+      <c r="F6">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="G6">
+        <v>88.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>90.7</v>
-      </c>
-      <c r="C6">
-        <v>47.5</v>
-      </c>
-      <c r="D6">
-        <v>91</v>
-      </c>
-      <c r="E6">
+      <c r="B7">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="C7">
+        <v>46.2</v>
+      </c>
+      <c r="D7">
+        <v>92.2</v>
+      </c>
+      <c r="E7">
         <v>75.09999999999999</v>
       </c>
-      <c r="F6">
-        <v>71.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="C7">
-        <v>37.6</v>
-      </c>
-      <c r="D7">
-        <v>9.6</v>
-      </c>
-      <c r="E7">
-        <v>66.5</v>
-      </c>
       <c r="F7">
-        <v>70.39999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>60.8</v>
+      </c>
+      <c r="G7">
+        <v>69.59999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>2.4</v>
+      </c>
+      <c r="C8">
+        <v>74.3</v>
+      </c>
+      <c r="D8">
+        <v>19</v>
+      </c>
+      <c r="E8">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>15.2</v>
+      </c>
+      <c r="G8">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="B8">
-        <v>41.5</v>
-      </c>
-      <c r="C8">
-        <v>13.9</v>
-      </c>
-      <c r="D8">
-        <v>7.5</v>
-      </c>
-      <c r="E8">
-        <v>26.9</v>
-      </c>
-      <c r="F8">
-        <v>25.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9">
-        <v>2.2</v>
-      </c>
-      <c r="C9">
-        <v>72.5</v>
-      </c>
-      <c r="D9">
-        <v>22.6</v>
-      </c>
-      <c r="E9">
-        <v>22.2</v>
-      </c>
       <c r="F9">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>17</v>
+      </c>
+      <c r="G9">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B10">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C10">
-        <v>15.5</v>
+        <v>14.7</v>
       </c>
       <c r="D10">
-        <v>47</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="E10">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="F10">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>14.3</v>
+      </c>
+      <c r="G10">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>34.3</v>
+      </c>
+      <c r="C11">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>6.4</v>
+      </c>
+      <c r="E11">
+        <v>28.1</v>
+      </c>
+      <c r="F11">
+        <v>11.1</v>
+      </c>
+      <c r="G11">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>1.1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0.3</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>4.6</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
-        <v>35.4</v>
-      </c>
-      <c r="C11">
-        <v>53.40000000000001</v>
-      </c>
-      <c r="D11">
-        <v>48.6</v>
-      </c>
-      <c r="E11">
-        <v>4</v>
-      </c>
-      <c r="F11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12">
-        <v>0.2</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0.8</v>
-      </c>
-      <c r="F12">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="B13">
-        <v>0.6</v>
+        <v>39.6</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>53.2</v>
       </c>
       <c r="D13">
-        <v>0.3</v>
+        <v>50.2</v>
       </c>
       <c r="E13">
-        <v>0.1</v>
+        <v>4.7</v>
       </c>
       <c r="F13">
-        <v>0.1</v>
+        <v>1.2</v>
+      </c>
+      <c r="G13">
+        <v>0.7000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2760,28 +2883,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2789,28 +2912,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2">
-        <v>126.04</v>
+        <v>108.11</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>119.57</v>
+        <v>123.12</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.511</v>
       </c>
       <c r="H2">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2818,28 +2941,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3">
-        <v>95.98999999999999</v>
+        <v>105.09</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>119.57</v>
+        <v>124.17</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="H3">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2847,28 +2970,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4">
-        <v>106.38</v>
+        <v>110.07</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
       </c>
       <c r="F4">
-        <v>120.11</v>
+        <v>121.46</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="H4">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2876,28 +2999,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D5">
-        <v>110.25</v>
+        <v>132.54</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>120.11</v>
+        <v>121.37</v>
       </c>
       <c r="G5">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="H5">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2905,28 +3028,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6">
-        <v>112.22</v>
+        <v>119.51</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>118.46</v>
+        <v>122.73</v>
       </c>
       <c r="G6">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2934,28 +3057,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D7">
-        <v>120.86</v>
+        <v>105.85</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7">
-        <v>118.46</v>
+        <v>120.39</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="H7">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2966,25 +3089,25 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D8">
-        <v>99.81999999999999</v>
+        <v>108.63</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>119.51</v>
+        <v>121.26</v>
       </c>
       <c r="G8">
-        <v>0.525</v>
+        <v>0.489</v>
       </c>
       <c r="H8">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2992,28 +3115,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D9">
-        <v>122.78</v>
+        <v>118.94</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>119.51</v>
+        <v>121.18</v>
       </c>
       <c r="G9">
-        <v>0.525</v>
+        <v>0.578</v>
       </c>
       <c r="H9">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3021,28 +3144,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10">
-        <v>122.28</v>
+        <v>121.33</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>117.43</v>
+        <v>117.68</v>
       </c>
       <c r="G10">
-        <v>0.55</v>
+        <v>0.489</v>
       </c>
       <c r="H10">
-        <v>-1.1</v>
+        <v>-2.7</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3053,25 +3176,25 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D11">
-        <v>121.17</v>
+        <v>125.4</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>117.43</v>
+        <v>118.1</v>
       </c>
       <c r="G11">
-        <v>0.55</v>
+        <v>0.511</v>
       </c>
       <c r="H11">
-        <v>-1.1</v>
+        <v>-2.9</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3082,25 +3205,25 @@
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D12">
-        <v>136.69</v>
+        <v>133.63</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
       <c r="F12">
-        <v>113.78</v>
+        <v>114.45</v>
       </c>
       <c r="G12">
-        <v>0.425</v>
+        <v>0.422</v>
       </c>
       <c r="H12">
-        <v>-1.8</v>
+        <v>-3.7</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3111,25 +3234,25 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D13">
-        <v>143.25</v>
+        <v>151.73</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>113.78</v>
+        <v>114.9</v>
       </c>
       <c r="G13">
-        <v>0.425</v>
+        <v>0.444</v>
       </c>
       <c r="H13">
-        <v>-1.8</v>
+        <v>-4.1</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3144,31 +3267,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3176,28 +3299,28 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D2">
-        <v>143.245</v>
+        <v>151.728</v>
       </c>
       <c r="E2">
-        <v>572.98</v>
+        <v>758.64</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3205,16 +3328,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D3">
-        <v>136.685</v>
+        <v>133.628</v>
       </c>
       <c r="E3">
-        <v>546.74</v>
+        <v>668.14</v>
       </c>
       <c r="F3">
         <v>99.8</v>
@@ -3223,10 +3346,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3234,289 +3357,289 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>126.04</v>
+        <v>132.544</v>
       </c>
       <c r="E4">
-        <v>504.16</v>
+        <v>662.72</v>
       </c>
       <c r="F4">
-        <v>97.8</v>
+        <v>99.8</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D5">
-        <v>120.855</v>
+        <v>125.396</v>
       </c>
       <c r="E5">
-        <v>483.42</v>
+        <v>626.98</v>
       </c>
       <c r="F5">
-        <v>92.7</v>
+        <v>90.2</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D6">
-        <v>122.775</v>
+        <v>119.508</v>
       </c>
       <c r="E6">
-        <v>491.1</v>
+        <v>597.54</v>
       </c>
       <c r="F6">
-        <v>71.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C7">
+        <v>0.4</v>
+      </c>
+      <c r="D7">
+        <v>121.328</v>
+      </c>
+      <c r="E7">
+        <v>606.64</v>
+      </c>
+      <c r="F7">
+        <v>67.60000000000001</v>
+      </c>
+      <c r="G7">
         <v>0.5</v>
       </c>
-      <c r="D7">
-        <v>121.165</v>
-      </c>
-      <c r="E7">
-        <v>484.6600000000001</v>
-      </c>
-      <c r="F7">
-        <v>69.8</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D8">
-        <v>122.285</v>
+        <v>110.072</v>
       </c>
       <c r="E8">
-        <v>489.14</v>
+        <v>550.36</v>
       </c>
       <c r="F8">
-        <v>26.1</v>
+        <v>16.1</v>
       </c>
       <c r="G8">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="H8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D9">
-        <v>110.25</v>
+        <v>105.092</v>
       </c>
       <c r="E9">
-        <v>441</v>
+        <v>525.46</v>
       </c>
       <c r="F9">
-        <v>22.9</v>
+        <v>14.2</v>
       </c>
       <c r="G9">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="H9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>106.38</v>
+        <v>108.628</v>
       </c>
       <c r="E10">
-        <v>425.52</v>
+        <v>543.14</v>
       </c>
       <c r="F10">
-        <v>11.6</v>
+        <v>13.8</v>
       </c>
       <c r="G10">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>112.215</v>
+        <v>118.936</v>
       </c>
       <c r="E11">
-        <v>448.86</v>
+        <v>594.6799999999999</v>
       </c>
       <c r="F11">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="G11">
-        <v>7.6</v>
+        <v>11.8</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C12">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D12">
-        <v>99.81999999999999</v>
+        <v>105.852</v>
       </c>
       <c r="E12">
-        <v>399.28</v>
+        <v>529.26</v>
       </c>
       <c r="F12">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="G12">
-        <v>19.1</v>
+        <v>22.7</v>
       </c>
       <c r="H12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>95.98999999999999</v>
+        <v>108.112</v>
       </c>
       <c r="E13">
-        <v>383.96</v>
+        <v>540.5600000000001</v>
       </c>
       <c r="F13">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="G13">
-        <v>68.30000000000001</v>
+        <v>50.8</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3531,19 +3654,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3554,16 +3677,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3571,19 +3694,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3591,19 +3714,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3611,19 +3734,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
         <v>60</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3634,16 +3757,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3651,19 +3774,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3671,19 +3794,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3694,16 +3817,16 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D9">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3714,16 +3837,16 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3731,19 +3854,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D11">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3754,7 +3877,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12">
         <v>-12</v>
@@ -3763,7 +3886,7 @@
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3771,19 +3894,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13">
-        <v>-12</v>
+        <v>-18</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -3793,27 +3916,30 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>112</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3829,71 +3955,83 @@
       <c r="E2">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="F2">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
         <v>9</v>
       </c>
-      <c r="F3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>-2</v>
+      </c>
+      <c r="C5">
+        <v>-5</v>
+      </c>
+      <c r="D5">
+        <v>-5</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>-2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>7</v>
-      </c>
-      <c r="E4">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -3909,51 +4047,60 @@
       <c r="E6">
         <v>6</v>
       </c>
-      <c r="F6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B7">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="C7">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="D7">
         <v>-5</v>
       </c>
       <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>-2</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
         <v>3</v>
       </c>
-      <c r="B8">
-        <v>-4</v>
-      </c>
       <c r="C8">
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>-5</v>
+        <v>14</v>
       </c>
       <c r="E8">
+        <v>9</v>
+      </c>
+      <c r="F8">
         <v>-2</v>
       </c>
-      <c r="F8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -3969,11 +4116,14 @@
       <c r="E9">
         <v>-5</v>
       </c>
-      <c r="F9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="F9">
+        <v>-2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -3989,31 +4139,37 @@
       <c r="E10">
         <v>-6</v>
       </c>
-      <c r="F10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10">
+        <v>-5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B11">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="C11">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="D11">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="E11">
-        <v>-9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>-12</v>
+      </c>
+      <c r="F11">
+        <v>-11</v>
+      </c>
+      <c r="G11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -4029,28 +4185,34 @@
       <c r="E12">
         <v>-12</v>
       </c>
-      <c r="F12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="F12">
+        <v>-12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B13">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="C13">
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="D13">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="E13">
-        <v>-12</v>
-      </c>
-      <c r="F13" t="s">
-        <v>106</v>
+        <v>-9</v>
+      </c>
+      <c r="F13">
+        <v>-18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Family Fantasy 2026.xlsx
+++ b/data/leagues/Family Fantasy 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="122">
   <si>
     <t>Noah's Nifty Team</t>
   </si>
@@ -61,25 +61,31 @@
     <t>That movie was great...</t>
   </si>
   <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>1-4-0</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>0-5-0</t>
-  </si>
-  <si>
-    <t>1-3-1</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>0-6-0</t>
+  </si>
+  <si>
+    <t>1-4-1</t>
+  </si>
+  <si>
+    <t>6-0-0</t>
+  </si>
+  <si>
+    <t>2-3-1</t>
   </si>
   <si>
     <t>Teams</t>
@@ -157,6 +163,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -184,10 +193,13 @@
     <t>lawrence wallach</t>
   </si>
   <si>
+    <t>Gabe Musty</t>
+  </si>
+  <si>
     <t>Louis Rodriguez</t>
   </si>
   <si>
-    <t>Gabe Musty</t>
+    <t>Jordan Wallach</t>
   </si>
   <si>
     <t>Zach Wallach</t>
@@ -196,24 +208,21 @@
     <t>D Swizzle</t>
   </si>
   <si>
-    <t>Jordan Wallach</t>
-  </si>
-  <si>
     <t>Michael Dickert</t>
   </si>
   <si>
+    <t>Jackson Jansorn</t>
+  </si>
+  <si>
+    <t>Ted Wallach</t>
+  </si>
+  <si>
     <t>Kari Dickert</t>
   </si>
   <si>
-    <t>Jackson Jansorn</t>
-  </si>
-  <si>
     <t>Noah Wallach</t>
   </si>
   <si>
-    <t>Ted Wallach</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -238,52 +247,58 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>5-0</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>0-5</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>11.6-2.4-0.1</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>6-0</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>0-6</t>
+  </si>
+  <si>
+    <t>11.3-2.6-0.1</t>
   </si>
   <si>
     <t>10.6-3.4-0.1</t>
   </si>
   <si>
-    <t>10.6-3.3-0.1</t>
-  </si>
-  <si>
-    <t>8.2-5.7-0.1</t>
-  </si>
-  <si>
-    <t>6.9-7.0-0.1</t>
-  </si>
-  <si>
-    <t>5.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>5.3-8.6-0.1</t>
-  </si>
-  <si>
-    <t>4.2-9.7-0.1</t>
-  </si>
-  <si>
-    <t>4.1-9.8-0.1</t>
-  </si>
-  <si>
-    <t>2.9-11.0-0.1</t>
+    <t>10.3-3.6-0.1</t>
+  </si>
+  <si>
+    <t>8.9-5.0-0.1</t>
+  </si>
+  <si>
+    <t>9.0-4.9-0.1</t>
+  </si>
+  <si>
+    <t>6.5-7.4-0.1</t>
+  </si>
+  <si>
+    <t>6.1-7.8-0.1</t>
+  </si>
+  <si>
+    <t>5.0-9.0-0.1</t>
+  </si>
+  <si>
+    <t>5.2-8.7-0.1</t>
+  </si>
+  <si>
+    <t>4.6-9.3-0.1</t>
+  </si>
+  <si>
+    <t>3.7-10.2-0.1</t>
+  </si>
+  <si>
+    <t>2.3-11.6-0.1</t>
   </si>
   <si>
     <t>12-2</t>
@@ -295,22 +310,16 @@
     <t>9-5</t>
   </si>
   <si>
-    <t>8-6</t>
-  </si>
-  <si>
-    <t>7-7</t>
+    <t>6-8</t>
   </si>
   <si>
     <t>5-9</t>
   </si>
   <si>
-    <t>6-8</t>
-  </si>
-  <si>
     <t>4-10</t>
   </si>
   <si>
-    <t>3-11</t>
+    <t>2-12</t>
   </si>
   <si>
     <t>Owners</t>
@@ -322,13 +331,13 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑2</t>
+  </si>
+  <si>
     <t>↑1</t>
   </si>
   <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↑6</t>
+    <t>0</t>
   </si>
   <si>
     <t>↑3</t>
@@ -337,16 +346,10 @@
     <t>↓1</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↓11</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↓9</t>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↓8</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -362,6 +365,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -792,19 +798,19 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -836,7 +842,7 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
@@ -848,10 +854,10 @@
         <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K3" t="s">
         <v>14</v>
@@ -883,16 +889,16 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K4" t="s">
         <v>14</v>
@@ -912,37 +918,37 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
+      <c r="H5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>13</v>
-      </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -953,28 +959,28 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" t="s">
         <v>15</v>
       </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" t="s">
-        <v>13</v>
-      </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K6" t="s">
         <v>12</v>
@@ -983,7 +989,7 @@
         <v>15</v>
       </c>
       <c r="M6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -994,28 +1000,28 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K7" t="s">
         <v>15</v>
@@ -1024,7 +1030,7 @@
         <v>14</v>
       </c>
       <c r="M7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1041,22 +1047,22 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K8" t="s">
         <v>12</v>
@@ -1065,7 +1071,7 @@
         <v>13</v>
       </c>
       <c r="M8" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1076,37 +1082,37 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
       </c>
       <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" t="s">
         <v>15</v>
-      </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1114,40 +1120,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" t="s">
-        <v>13</v>
-      </c>
       <c r="I10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1179,7 +1185,7 @@
         <v>12</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K11" t="s">
         <v>13</v>
@@ -1196,40 +1202,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" t="s">
         <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" t="s">
-        <v>16</v>
-      </c>
-      <c r="M12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1246,22 +1252,22 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
       </c>
       <c r="I13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K13" t="s">
         <v>14</v>
@@ -1280,30 +1286,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1311,22 +1317,22 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -1337,25 +1343,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3">
-        <v>-18</v>
+        <v>-12</v>
       </c>
       <c r="F3">
-        <v>-2</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1389,25 +1395,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>-18</v>
       </c>
       <c r="F5">
         <v>-2</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1415,22 +1421,22 @@
         <v>4</v>
       </c>
       <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
       <c r="D6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>-17</v>
       </c>
       <c r="F6">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>2</v>
@@ -1441,25 +1447,25 @@
         <v>5</v>
       </c>
       <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>5</v>
-      </c>
       <c r="E7">
-        <v>-9</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1467,25 +1473,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>-7</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1496,22 +1502,22 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E9">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="F9">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1519,25 +1525,25 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>7</v>
+      </c>
+      <c r="H10" t="s">
         <v>8</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-      <c r="H10" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1545,24 +1551,50 @@
         <v>9</v>
       </c>
       <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
         <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
       </c>
       <c r="D11" t="s">
         <v>1</v>
       </c>
       <c r="E11">
+        <v>-7</v>
+      </c>
+      <c r="F11">
+        <v>-2</v>
+      </c>
+      <c r="G11">
         <v>5</v>
       </c>
-      <c r="F11">
-        <v>6</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
       <c r="H11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12">
+        <v>13</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1578,13 +1610,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1592,13 +1624,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>1.5</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1606,13 +1638,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>1.833333333333333</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1620,13 +1652,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1.833333333333333</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1634,13 +1666,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>1.916666666666667</v>
+        <v>2.5</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1648,13 +1680,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1662,13 +1694,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>2.25</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1679,10 +1711,10 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>2.583333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1690,13 +1722,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>2.75</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1704,10 +1736,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>2.916666666666667</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1721,7 +1753,7 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>3.166666666666667</v>
+        <v>3.916666666666667</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1732,13 +1764,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12">
         <v>4</v>
       </c>
-      <c r="C12">
-        <v>3.583333333333333</v>
-      </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1746,13 +1778,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>3.583333333333333</v>
+        <v>4.5</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1767,16 +1799,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1784,13 +1816,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>3.916666666666667</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="D2">
-        <v>-0.08333333333333348</v>
+        <v>-0.166666666666667</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1801,16 +1833,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>3.833333333333333</v>
+        <v>4.416666666666667</v>
       </c>
       <c r="D3">
-        <v>-0.1666666666666665</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1821,13 +1853,13 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>3.416666666666667</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="D4">
-        <v>-1.583333333333333</v>
+        <v>-2.166666666666667</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1835,16 +1867,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>2.833333333333333</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="D5">
-        <v>0.8333333333333335</v>
+        <v>-0.4166666666666665</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1852,16 +1884,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>2.666666666666667</v>
+        <v>3.25</v>
       </c>
       <c r="D6">
-        <v>-0.3333333333333335</v>
+        <v>-1.75</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1869,16 +1901,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>2.583333333333333</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D7">
-        <v>-1.416666666666667</v>
+        <v>0.9166666666666665</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1886,16 +1918,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1.916666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D8">
-        <v>-0.08333333333333326</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1903,16 +1935,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>1.916666666666667</v>
+        <v>2.5</v>
       </c>
       <c r="D9">
-        <v>1.916666666666667</v>
+        <v>-1.5</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1923,13 +1955,13 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>1.833333333333333</v>
+        <v>2.25</v>
       </c>
       <c r="D10">
-        <v>-0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1937,16 +1969,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>1.666666666666667</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D11">
-        <v>-1.333333333333333</v>
+        <v>0.08333333333333348</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1957,13 +1989,13 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>1.666666666666667</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="D12">
-        <v>0.6666666666666667</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1980,7 +2012,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1995,69 +2027,69 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>66.40000000000001</v>
+        <v>48.9</v>
       </c>
       <c r="C2">
-        <v>23.6</v>
+        <v>29.5</v>
       </c>
       <c r="D2">
-        <v>8.6</v>
+        <v>14.9</v>
       </c>
       <c r="E2">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="F2">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -2083,28 +2115,28 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>14.8</v>
+        <v>30.7</v>
       </c>
       <c r="C3">
-        <v>34.6</v>
+        <v>35.8</v>
       </c>
       <c r="D3">
-        <v>37.1</v>
+        <v>20.5</v>
       </c>
       <c r="E3">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="F3">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="G3">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2122,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -2130,28 +2162,28 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>17.6</v>
+        <v>15.4</v>
       </c>
       <c r="C4">
-        <v>33.9</v>
+        <v>20.7</v>
       </c>
       <c r="D4">
-        <v>32.1</v>
+        <v>28.9</v>
       </c>
       <c r="E4">
-        <v>11.3</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>11.9</v>
       </c>
       <c r="G4">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="H4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2166,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>99.8</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -2174,43 +2206,43 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="C5">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>20.5</v>
       </c>
       <c r="E5">
-        <v>34.8</v>
+        <v>32.4</v>
       </c>
       <c r="F5">
-        <v>24.2</v>
+        <v>28.3</v>
       </c>
       <c r="G5">
-        <v>15.1</v>
+        <v>6.9</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="I5">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="K5">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>90.2</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2218,92 +2250,92 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="C6">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="D6">
-        <v>7.3</v>
+        <v>14.1</v>
       </c>
       <c r="E6">
-        <v>25.4</v>
+        <v>27.4</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>35.6</v>
       </c>
       <c r="G6">
-        <v>16.2</v>
+        <v>9</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>2.3</v>
       </c>
       <c r="I6">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J6">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="K6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>87.3</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.1</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.5</v>
       </c>
-      <c r="D7">
-        <v>2.6</v>
-      </c>
       <c r="E7">
-        <v>13</v>
+        <v>2.1</v>
       </c>
       <c r="F7">
-        <v>22.7</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>28.7</v>
+        <v>26.6</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>26.3</v>
       </c>
       <c r="I7">
-        <v>8.5</v>
+        <v>19.1</v>
       </c>
       <c r="J7">
-        <v>4.3</v>
+        <v>11.4</v>
       </c>
       <c r="K7">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="L7">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="M7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>67.59999999999999</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2312,42 +2344,42 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E8">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="F8">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G8">
-        <v>10.9</v>
+        <v>25.7</v>
       </c>
       <c r="H8">
-        <v>20.5</v>
+        <v>23.4</v>
       </c>
       <c r="I8">
-        <v>17.9</v>
+        <v>18.6</v>
       </c>
       <c r="J8">
-        <v>17.7</v>
+        <v>12.8</v>
       </c>
       <c r="K8">
-        <v>14.2</v>
+        <v>6.1</v>
       </c>
       <c r="L8">
-        <v>9.4</v>
+        <v>2.5</v>
       </c>
       <c r="M8">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="N8">
-        <v>16.1</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2356,42 +2388,42 @@
         <v>0</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>0.2</v>
       </c>
-      <c r="E9">
-        <v>0.9</v>
-      </c>
       <c r="F9">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="G9">
-        <v>9.699999999999999</v>
+        <v>14</v>
       </c>
       <c r="H9">
-        <v>14.2</v>
+        <v>17.7</v>
       </c>
       <c r="I9">
-        <v>20.3</v>
+        <v>18.9</v>
       </c>
       <c r="J9">
-        <v>18.5</v>
+        <v>19.6</v>
       </c>
       <c r="K9">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
       <c r="L9">
-        <v>12.6</v>
+        <v>7.8</v>
       </c>
       <c r="M9">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="N9">
-        <v>14.2</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2400,42 +2432,42 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E10">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="F10">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="G10">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H10">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="I10">
-        <v>19.5</v>
+        <v>21.7</v>
       </c>
       <c r="J10">
-        <v>17.2</v>
+        <v>20.4</v>
       </c>
       <c r="K10">
-        <v>15.3</v>
+        <v>18.5</v>
       </c>
       <c r="L10">
-        <v>10.9</v>
+        <v>7.8</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="N10">
-        <v>13.8</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2447,34 +2479,34 @@
         <v>0</v>
       </c>
       <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>0.5</v>
       </c>
-      <c r="F11">
-        <v>1.3</v>
-      </c>
       <c r="G11">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H11">
-        <v>10.9</v>
+        <v>7.5</v>
       </c>
       <c r="I11">
-        <v>14.9</v>
+        <v>12.5</v>
       </c>
       <c r="J11">
-        <v>17</v>
+        <v>20.7</v>
       </c>
       <c r="K11">
-        <v>19.8</v>
+        <v>26.3</v>
       </c>
       <c r="L11">
-        <v>19.3</v>
+        <v>21</v>
       </c>
       <c r="M11">
-        <v>11.8</v>
+        <v>6.8</v>
       </c>
       <c r="N11">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2491,34 +2523,34 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="H12">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="J12">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="K12">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="L12">
-        <v>24.1</v>
+        <v>38.4</v>
       </c>
       <c r="M12">
-        <v>22.7</v>
+        <v>20</v>
       </c>
       <c r="N12">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2535,34 +2567,34 @@
         <v>0</v>
       </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>0.1</v>
       </c>
-      <c r="F13">
-        <v>0.2</v>
-      </c>
-      <c r="G13">
-        <v>0.9</v>
-      </c>
       <c r="H13">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="I13">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J13">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>12.3</v>
+        <v>6.3</v>
       </c>
       <c r="L13">
-        <v>22.5</v>
+        <v>21.2</v>
       </c>
       <c r="M13">
-        <v>50.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="N13">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2572,35 +2604,38 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>45</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2612,18 +2647,21 @@
         <v>99.90000000000001</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -2632,243 +2670,276 @@
         <v>100</v>
       </c>
       <c r="E3">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="F3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>99.90000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>23.2</v>
+        <v>21.5</v>
       </c>
       <c r="C4">
-        <v>71.39999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="D4">
-        <v>83.89999999999999</v>
+        <v>84.39999999999999</v>
       </c>
       <c r="E4">
-        <v>98.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F4">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="G4">
-        <v>99.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>99.59999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>100</v>
       </c>
       <c r="C5">
-        <v>36.6</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D5">
-        <v>11.8</v>
+        <v>89.5</v>
       </c>
       <c r="E5">
-        <v>67.10000000000001</v>
+        <v>93.30000000000001</v>
       </c>
       <c r="F5">
-        <v>87.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="G5">
-        <v>88.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="H5">
+        <v>96.39999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C6">
-        <v>89.60000000000001</v>
+        <v>35.2</v>
       </c>
       <c r="D6">
-        <v>89.8</v>
+        <v>10.8</v>
       </c>
       <c r="E6">
-        <v>92.30000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="F6">
-        <v>88.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="G6">
-        <v>88.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>96.7</v>
+      </c>
+      <c r="H6">
+        <v>96.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>7.3</v>
+      </c>
+      <c r="C7">
+        <v>15.8</v>
+      </c>
+      <c r="D7">
+        <v>48.9</v>
+      </c>
+      <c r="E7">
+        <v>13.8</v>
+      </c>
+      <c r="F7">
+        <v>15.2</v>
+      </c>
+      <c r="G7">
+        <v>43.4</v>
+      </c>
+      <c r="H7">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="C7">
-        <v>46.2</v>
-      </c>
-      <c r="D7">
-        <v>92.2</v>
-      </c>
-      <c r="E7">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="F7">
-        <v>60.8</v>
-      </c>
-      <c r="G7">
-        <v>69.59999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
+      <c r="B8">
+        <v>90.10000000000001</v>
+      </c>
+      <c r="C8">
+        <v>48.8</v>
+      </c>
+      <c r="D8">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="E8">
+        <v>75.7</v>
+      </c>
+      <c r="F8">
+        <v>61.6</v>
+      </c>
+      <c r="G8">
+        <v>28.4</v>
+      </c>
+      <c r="H8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>35.6</v>
+      </c>
+      <c r="C9">
+        <v>14.3</v>
+      </c>
+      <c r="D9">
+        <v>8.4</v>
+      </c>
+      <c r="E9">
+        <v>24</v>
+      </c>
+      <c r="F9">
+        <v>13.6</v>
+      </c>
+      <c r="G9">
+        <v>19.9</v>
+      </c>
+      <c r="H9">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B8">
-        <v>2.4</v>
-      </c>
-      <c r="C8">
-        <v>74.3</v>
-      </c>
-      <c r="D8">
-        <v>19</v>
-      </c>
-      <c r="E8">
+      <c r="B10">
+        <v>3.9</v>
+      </c>
+      <c r="C10">
+        <v>73.5</v>
+      </c>
+      <c r="D10">
         <v>22</v>
       </c>
-      <c r="F8">
-        <v>15.2</v>
-      </c>
-      <c r="G8">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
+      <c r="E10">
+        <v>24.2</v>
+      </c>
+      <c r="F10">
+        <v>13.2</v>
+      </c>
+      <c r="G10">
+        <v>12.2</v>
+      </c>
+      <c r="H10">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>17</v>
-      </c>
-      <c r="G9">
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="C10">
-        <v>14.7</v>
-      </c>
-      <c r="D10">
-        <v>46.40000000000001</v>
-      </c>
-      <c r="E10">
-        <v>11.6</v>
-      </c>
-      <c r="F10">
-        <v>14.3</v>
-      </c>
-      <c r="G10">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B11">
-        <v>34.3</v>
+        <v>0.2</v>
       </c>
       <c r="C11">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>28.1</v>
+        <v>0.8</v>
       </c>
       <c r="F11">
-        <v>11.1</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>5.1</v>
+      </c>
+      <c r="H11">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B12">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="G12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B13">
-        <v>39.6</v>
+        <v>40.9</v>
       </c>
       <c r="C13">
-        <v>53.2</v>
+        <v>50.7</v>
       </c>
       <c r="D13">
-        <v>50.2</v>
+        <v>44.4</v>
       </c>
       <c r="E13">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>1.2</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="G13">
-        <v>0.7000000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2883,28 +2954,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2915,25 +2986,25 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D2">
-        <v>108.11</v>
+        <v>99.48</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>123.12</v>
+        <v>119.43</v>
       </c>
       <c r="G2">
-        <v>0.511</v>
+        <v>0.438</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2944,25 +3015,25 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D3">
-        <v>105.09</v>
+        <v>107.82</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
       </c>
       <c r="F3">
-        <v>124.17</v>
+        <v>123.32</v>
       </c>
       <c r="G3">
-        <v>0.556</v>
+        <v>0.583</v>
       </c>
       <c r="H3">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2970,28 +3041,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>110.07</v>
+        <v>125.34</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>121.46</v>
+        <v>121.27</v>
       </c>
       <c r="G4">
-        <v>0.444</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H4">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2999,28 +3070,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D5">
-        <v>132.54</v>
+        <v>109.43</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>121.37</v>
+        <v>118.17</v>
       </c>
       <c r="G5">
-        <v>0.489</v>
+        <v>0.479</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3028,28 +3099,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D6">
-        <v>119.51</v>
+        <v>103.52</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>122.73</v>
+        <v>120.38</v>
       </c>
       <c r="G6">
-        <v>0.533</v>
+        <v>0.479</v>
       </c>
       <c r="H6">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3057,28 +3128,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D7">
-        <v>105.85</v>
+        <v>118.68</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>120.39</v>
+        <v>117.46</v>
       </c>
       <c r="G7">
-        <v>0.533</v>
+        <v>0.521</v>
       </c>
       <c r="H7">
         <v>0.9</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3086,28 +3157,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D8">
-        <v>108.63</v>
+        <v>102.37</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>121.26</v>
+        <v>116.7</v>
       </c>
       <c r="G8">
-        <v>0.489</v>
+        <v>0.5</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3118,25 +3189,25 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D9">
-        <v>118.94</v>
+        <v>118.79</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
       </c>
       <c r="F9">
-        <v>121.18</v>
+        <v>118.69</v>
       </c>
       <c r="G9">
-        <v>0.578</v>
+        <v>0.583</v>
       </c>
       <c r="H9">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3144,28 +3215,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10">
+        <v>126.64</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>115.42</v>
+      </c>
+      <c r="G10">
+        <v>0.521</v>
+      </c>
+      <c r="H10">
+        <v>-3</v>
+      </c>
+      <c r="I10">
         <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10">
-        <v>121.33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10">
-        <v>117.68</v>
-      </c>
-      <c r="G10">
-        <v>0.489</v>
-      </c>
-      <c r="H10">
-        <v>-2.7</v>
-      </c>
-      <c r="I10">
-        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3173,28 +3244,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D11">
-        <v>125.4</v>
+        <v>145.38</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
       <c r="F11">
-        <v>118.1</v>
+        <v>111.67</v>
       </c>
       <c r="G11">
-        <v>0.511</v>
+        <v>0.417</v>
       </c>
       <c r="H11">
-        <v>-2.9</v>
+        <v>-3.9</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3202,28 +3273,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D12">
-        <v>133.63</v>
+        <v>113.73</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>114.45</v>
+        <v>113.57</v>
       </c>
       <c r="G12">
-        <v>0.422</v>
+        <v>0.479</v>
       </c>
       <c r="H12">
-        <v>-3.7</v>
+        <v>-4.9</v>
       </c>
       <c r="I12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3231,28 +3302,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D13">
-        <v>151.73</v>
+        <v>135.6</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
       </c>
       <c r="F13">
-        <v>114.9</v>
+        <v>110.68</v>
       </c>
       <c r="G13">
-        <v>0.444</v>
+        <v>0.438</v>
       </c>
       <c r="H13">
-        <v>-4.1</v>
+        <v>-6.4</v>
       </c>
       <c r="I13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3267,48 +3338,48 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D2">
-        <v>151.728</v>
+        <v>135.6033333333333</v>
       </c>
       <c r="E2">
-        <v>758.64</v>
+        <v>813.62</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -3317,39 +3388,39 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>133.628</v>
+        <v>145.3833333333333</v>
       </c>
       <c r="E3">
-        <v>668.14</v>
+        <v>872.3</v>
       </c>
       <c r="F3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3357,28 +3428,28 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>132.544</v>
+        <v>125.3366666666667</v>
       </c>
       <c r="E4">
-        <v>662.72</v>
+        <v>752.02</v>
       </c>
       <c r="F4">
-        <v>99.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3386,28 +3457,28 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>125.396</v>
+        <v>126.6433333333333</v>
       </c>
       <c r="E5">
-        <v>626.98</v>
+        <v>759.86</v>
       </c>
       <c r="F5">
-        <v>90.2</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3415,173 +3486,173 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C6">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D6">
-        <v>119.508</v>
+        <v>118.6766666666667</v>
       </c>
       <c r="E6">
-        <v>597.54</v>
+        <v>712.0599999999999</v>
       </c>
       <c r="F6">
-        <v>87.3</v>
+        <v>96.2</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D7">
-        <v>121.328</v>
+        <v>107.8166666666667</v>
       </c>
       <c r="E7">
-        <v>606.64</v>
+        <v>646.9000000000001</v>
       </c>
       <c r="F7">
-        <v>67.60000000000001</v>
+        <v>36.3</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>110.072</v>
+        <v>113.7266666666667</v>
       </c>
       <c r="E8">
-        <v>550.36</v>
+        <v>682.36</v>
       </c>
       <c r="F8">
-        <v>16.1</v>
+        <v>36.1</v>
       </c>
       <c r="G8">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="H8" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C9">
-        <v>0.6</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D9">
-        <v>105.092</v>
+        <v>118.7933333333333</v>
       </c>
       <c r="E9">
-        <v>525.46</v>
+        <v>712.76</v>
       </c>
       <c r="F9">
-        <v>14.2</v>
+        <v>16.6</v>
       </c>
       <c r="G9">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="H9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10">
-        <v>108.628</v>
+        <v>109.4333333333333</v>
       </c>
       <c r="E10">
-        <v>543.14</v>
+        <v>656.6</v>
       </c>
       <c r="F10">
-        <v>13.8</v>
+        <v>11.6</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D11">
-        <v>118.936</v>
+        <v>103.52</v>
       </c>
       <c r="E11">
-        <v>594.6799999999999</v>
+        <v>621.12</v>
       </c>
       <c r="F11">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="G11">
-        <v>11.8</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3589,28 +3660,28 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C12">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D12">
-        <v>105.852</v>
+        <v>102.3666666666667</v>
       </c>
       <c r="E12">
-        <v>529.26</v>
+        <v>614.2</v>
       </c>
       <c r="F12">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="G12">
-        <v>22.7</v>
+        <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3618,28 +3689,28 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>108.112</v>
+        <v>99.47666666666667</v>
       </c>
       <c r="E13">
-        <v>540.5600000000001</v>
+        <v>596.86</v>
       </c>
       <c r="F13">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="G13">
-        <v>50.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3654,19 +3725,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3677,16 +3748,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3694,19 +3765,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3714,19 +3785,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D4">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3737,16 +3808,16 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3757,16 +3828,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3777,16 +3848,16 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3794,19 +3865,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3817,16 +3888,16 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D9">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3834,19 +3905,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D10">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3854,19 +3925,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D11">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3874,19 +3945,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3897,16 +3968,16 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D13">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -3916,30 +3987,33 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>114</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3958,57 +4032,66 @@
       <c r="F2">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>12</v>
       </c>
-      <c r="G3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="G3">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
         <v>7</v>
       </c>
-      <c r="D4">
-        <v>9</v>
-      </c>
       <c r="E4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>12</v>
       </c>
-      <c r="G4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="G4">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -4027,11 +4110,14 @@
       <c r="F5">
         <v>8</v>
       </c>
-      <c r="G5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -4050,11 +4136,14 @@
       <c r="F6">
         <v>5</v>
       </c>
-      <c r="G6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -4073,34 +4162,40 @@
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="G7">
+        <v>-1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>-1</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>-6</v>
       </c>
       <c r="F8">
-        <v>-2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>-5</v>
+      </c>
+      <c r="G8">
+        <v>-4</v>
+      </c>
+      <c r="H8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -4119,80 +4214,92 @@
       <c r="F9">
         <v>-2</v>
       </c>
-      <c r="G9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="G9">
+        <v>-8</v>
+      </c>
+      <c r="H9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C10">
+        <v>-3</v>
+      </c>
+      <c r="D10">
+        <v>-9</v>
+      </c>
+      <c r="E10">
+        <v>-12</v>
+      </c>
+      <c r="F10">
+        <v>-12</v>
+      </c>
+      <c r="G10">
+        <v>-9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>14</v>
+      </c>
+      <c r="E11">
+        <v>9</v>
+      </c>
+      <c r="F11">
+        <v>-2</v>
+      </c>
+      <c r="G11">
+        <v>-10</v>
+      </c>
+      <c r="H11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D10">
-        <v>-1</v>
-      </c>
-      <c r="E10">
-        <v>-6</v>
-      </c>
-      <c r="F10">
-        <v>-5</v>
-      </c>
-      <c r="G10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11">
+      <c r="B12">
         <v>-4</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>-15</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>-12</v>
-      </c>
-      <c r="E11">
-        <v>-12</v>
-      </c>
-      <c r="F11">
-        <v>-11</v>
-      </c>
-      <c r="G11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>-3</v>
-      </c>
-      <c r="D12">
-        <v>-9</v>
       </c>
       <c r="E12">
         <v>-12</v>
       </c>
       <c r="F12">
-        <v>-12</v>
-      </c>
-      <c r="G12" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>-11</v>
+      </c>
+      <c r="G12">
+        <v>-10</v>
+      </c>
+      <c r="H12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
@@ -4211,8 +4318,11 @@
       <c r="F13">
         <v>-18</v>
       </c>
-      <c r="G13" t="s">
-        <v>107</v>
+      <c r="G13">
+        <v>-17</v>
+      </c>
+      <c r="H13" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Family Fantasy 2026.xlsx
+++ b/data/leagues/Family Fantasy 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="128">
   <si>
     <t>Noah's Nifty Team</t>
   </si>
@@ -61,31 +61,31 @@
     <t>That movie was great...</t>
   </si>
   <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>0-6-0</t>
-  </si>
-  <si>
-    <t>1-4-1</t>
-  </si>
-  <si>
-    <t>6-0-0</t>
-  </si>
-  <si>
-    <t>2-3-1</t>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>0-7-0</t>
+  </si>
+  <si>
+    <t>2-4-1</t>
+  </si>
+  <si>
+    <t>7-0-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -166,6 +166,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -190,36 +193,36 @@
     <t>Diana Wallach</t>
   </si>
   <si>
+    <t>Gabe Musty</t>
+  </si>
+  <si>
+    <t>Jordan Wallach</t>
+  </si>
+  <si>
+    <t>Louis Rodriguez</t>
+  </si>
+  <si>
     <t>lawrence wallach</t>
   </si>
   <si>
-    <t>Gabe Musty</t>
-  </si>
-  <si>
-    <t>Louis Rodriguez</t>
-  </si>
-  <si>
-    <t>Jordan Wallach</t>
+    <t>D Swizzle</t>
   </si>
   <si>
     <t>Zach Wallach</t>
   </si>
   <si>
-    <t>D Swizzle</t>
-  </si>
-  <si>
     <t>Michael Dickert</t>
   </si>
   <si>
+    <t>Ted Wallach</t>
+  </si>
+  <si>
+    <t>Kari Dickert</t>
+  </si>
+  <si>
     <t>Jackson Jansorn</t>
   </si>
   <si>
-    <t>Ted Wallach</t>
-  </si>
-  <si>
-    <t>Kari Dickert</t>
-  </si>
-  <si>
     <t>Noah Wallach</t>
   </si>
   <si>
@@ -247,75 +250,78 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>6-0</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>0-6</t>
-  </si>
-  <si>
-    <t>11.3-2.6-0.1</t>
-  </si>
-  <si>
-    <t>10.6-3.4-0.1</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>7-0</t>
+  </si>
+  <si>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>0-7</t>
+  </si>
+  <si>
+    <t>10.3-3.6</t>
+  </si>
+  <si>
+    <t>10.4-3.5-0.1</t>
   </si>
   <si>
     <t>10.3-3.6-0.1</t>
   </si>
   <si>
-    <t>8.9-5.0-0.1</t>
-  </si>
-  <si>
-    <t>9.0-4.9-0.1</t>
-  </si>
-  <si>
-    <t>6.5-7.4-0.1</t>
-  </si>
-  <si>
-    <t>6.1-7.8-0.1</t>
-  </si>
-  <si>
-    <t>5.0-9.0-0.1</t>
-  </si>
-  <si>
-    <t>5.2-8.7-0.1</t>
-  </si>
-  <si>
-    <t>4.6-9.3-0.1</t>
+    <t>10.1-3.8-0.1</t>
+  </si>
+  <si>
+    <t>9.4-4.5-0.1</t>
+  </si>
+  <si>
+    <t>5.6-8.3-0.1</t>
+  </si>
+  <si>
+    <t>6.2-7.7-0.1</t>
+  </si>
+  <si>
+    <t>6.0-7.9-0.1</t>
+  </si>
+  <si>
+    <t>5.4-8.5-0.1</t>
   </si>
   <si>
     <t>3.7-10.2-0.1</t>
   </si>
   <si>
-    <t>2.3-11.6-0.1</t>
-  </si>
-  <si>
-    <t>12-2</t>
+    <t>3.9-10.1-0.1</t>
+  </si>
+  <si>
+    <t>2.1-11.8-0.1</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
+    <t>10-4</t>
+  </si>
+  <si>
     <t>9-5</t>
   </si>
   <si>
     <t>6-8</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
     <t>4-10</t>
   </si>
   <si>
@@ -331,25 +337,34 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
     <t>↑2</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑3</t>
+    <t>↓2</t>
   </si>
   <si>
     <t>↓1</t>
   </si>
   <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↓8</t>
+    <t>↑7</t>
+  </si>
+  <si>
+    <t>↓11</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓9</t>
+  </si>
+  <si>
+    <t>↓4</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -368,6 +383,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -795,22 +813,22 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -819,7 +837,7 @@
         <v>13</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L2" t="s">
         <v>13</v>
@@ -836,37 +854,37 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" t="s">
-        <v>15</v>
-      </c>
       <c r="M3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -877,19 +895,19 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -918,7 +936,7 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -930,7 +948,7 @@
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -939,10 +957,10 @@
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L5" t="s">
         <v>14</v>
@@ -965,10 +983,10 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -1000,37 +1018,37 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" t="s">
         <v>13</v>
       </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>15</v>
       </c>
-      <c r="L7" t="s">
-        <v>14</v>
-      </c>
       <c r="M7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1041,22 +1059,22 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
         <v>13</v>
@@ -1065,7 +1083,7 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L8" t="s">
         <v>13</v>
@@ -1082,37 +1100,37 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" t="s">
         <v>15</v>
       </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
-        <v>14</v>
-      </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1123,22 +1141,22 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>19</v>
-      </c>
       <c r="G10" t="s">
         <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I10" t="s">
         <v>13</v>
@@ -1147,7 +1165,7 @@
         <v>14</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L10" t="s">
         <v>14</v>
@@ -1164,37 +1182,37 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" t="s">
         <v>13</v>
       </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" t="s">
-        <v>13</v>
-      </c>
-      <c r="L11" t="s">
-        <v>15</v>
-      </c>
       <c r="M11" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1211,10 +1229,10 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
@@ -1223,16 +1241,16 @@
         <v>14</v>
       </c>
       <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" t="s">
         <v>16</v>
-      </c>
-      <c r="J12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L12" t="s">
-        <v>17</v>
       </c>
       <c r="M12" t="s">
         <v>15</v>
@@ -1243,40 +1261,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="H13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" t="s">
         <v>13</v>
       </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" t="s">
         <v>15</v>
       </c>
-      <c r="H13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" t="s">
-        <v>16</v>
-      </c>
-      <c r="K13" t="s">
-        <v>14</v>
-      </c>
       <c r="L13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M13" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1286,30 +1304,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1343,22 +1361,22 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
       <c r="E3">
-        <v>-12</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>-2</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -1369,25 +1387,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>-12</v>
       </c>
       <c r="F4">
-        <v>-11</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1398,22 +1416,22 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>-18</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="G5">
         <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1421,19 +1439,19 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G6">
         <v>16</v>
@@ -1447,25 +1465,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>-17</v>
       </c>
       <c r="F7">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1473,25 +1491,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1499,25 +1517,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1528,22 +1546,22 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>-9</v>
+      </c>
+      <c r="F10">
+        <v>-1</v>
+      </c>
+      <c r="G10">
         <v>8</v>
       </c>
-      <c r="E10">
-        <v>14</v>
-      </c>
-      <c r="F10">
-        <v>7</v>
-      </c>
-      <c r="G10">
-        <v>7</v>
-      </c>
       <c r="H10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1554,22 +1572,22 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>-7</v>
+        <v>14</v>
       </c>
       <c r="F11">
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H11" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1577,25 +1595,77 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>-7</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
         <v>9</v>
+      </c>
+      <c r="E13">
+        <v>13</v>
+      </c>
+      <c r="F13">
+        <v>8</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>-17</v>
+      </c>
+      <c r="F14">
+        <v>-12</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1627,7 +1697,7 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>1.916666666666667</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -1641,10 +1711,10 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1652,13 +1722,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>2.166666666666667</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1669,10 +1739,10 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1680,13 +1750,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>2.583333333333333</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1694,13 +1764,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>2.666666666666667</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1708,13 +1778,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1722,13 +1792,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>3.333333333333333</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1736,10 +1806,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>3.583333333333333</v>
+        <v>4</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1750,13 +1820,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>3.916666666666667</v>
+        <v>4.416666666666667</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1764,13 +1834,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1781,10 +1851,10 @@
         <v>4</v>
       </c>
       <c r="C13">
-        <v>4.5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1819,10 +1889,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4.833333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="D2">
-        <v>-0.166666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1836,13 +1906,13 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>4.416666666666667</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="D3">
-        <v>0.416666666666667</v>
+        <v>-0.08333333333333304</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1850,16 +1920,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>3.833333333333333</v>
+        <v>4.5</v>
       </c>
       <c r="D4">
-        <v>-2.166666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1867,16 +1937,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>3.583333333333333</v>
+        <v>4.25</v>
       </c>
       <c r="D5">
-        <v>-0.4166666666666665</v>
+        <v>-1.75</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1884,16 +1954,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>-1.75</v>
+        <v>-3</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1901,13 +1971,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>2.916666666666667</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D7">
-        <v>0.9166666666666665</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -1918,16 +1988,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>2.666666666666667</v>
+        <v>3.25</v>
       </c>
       <c r="D8">
-        <v>1.666666666666667</v>
+        <v>1.25</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1935,16 +2005,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>2.5</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="D9">
-        <v>-1.5</v>
+        <v>0.08333333333333348</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1952,16 +2022,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="D10">
-        <v>0.25</v>
+        <v>-1.25</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1969,16 +2039,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>2.083333333333333</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D11">
-        <v>0.08333333333333348</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1986,16 +2056,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>1.916666666666667</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D12">
-        <v>0.9166666666666667</v>
+        <v>0.08333333333333348</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2006,13 +2076,13 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>1.666666666666667</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D13">
-        <v>1.666666666666667</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2071,25 +2141,25 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>48.9</v>
+        <v>33.7</v>
       </c>
       <c r="C2">
-        <v>29.5</v>
+        <v>25.5</v>
       </c>
       <c r="D2">
-        <v>14.9</v>
+        <v>18.3</v>
       </c>
       <c r="E2">
-        <v>5.1</v>
+        <v>13.3</v>
       </c>
       <c r="F2">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="G2">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -2115,28 +2185,28 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B3">
-        <v>30.7</v>
+        <v>23.5</v>
       </c>
       <c r="C3">
-        <v>35.8</v>
+        <v>28.9</v>
       </c>
       <c r="D3">
-        <v>20.5</v>
+        <v>23.6</v>
       </c>
       <c r="E3">
-        <v>9.6</v>
+        <v>16.1</v>
       </c>
       <c r="F3">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2154,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -2162,28 +2232,28 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="C4">
-        <v>20.7</v>
+        <v>17.1</v>
       </c>
       <c r="D4">
-        <v>28.9</v>
+        <v>19.1</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>22.6</v>
       </c>
       <c r="F4">
-        <v>11.9</v>
+        <v>19.7</v>
       </c>
       <c r="G4">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="H4">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2198,42 +2268,42 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5">
+        <v>16.2</v>
+      </c>
+      <c r="C5">
+        <v>16.6</v>
+      </c>
+      <c r="D5">
+        <v>20.9</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>23</v>
+      </c>
+      <c r="G5">
         <v>2.7</v>
       </c>
-      <c r="C5">
-        <v>6.1</v>
-      </c>
-      <c r="D5">
-        <v>20.5</v>
-      </c>
-      <c r="E5">
-        <v>32.4</v>
-      </c>
-      <c r="F5">
-        <v>28.3</v>
-      </c>
-      <c r="G5">
-        <v>6.9</v>
-      </c>
       <c r="H5">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2242,39 +2312,39 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>96.90000000000001</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>2.3</v>
+        <v>7.2</v>
       </c>
       <c r="C6">
-        <v>7.8</v>
+        <v>11.8</v>
       </c>
       <c r="D6">
-        <v>14.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6">
-        <v>27.4</v>
+        <v>26.1</v>
       </c>
       <c r="F6">
-        <v>35.6</v>
+        <v>32.1</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="I6">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J6">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -2286,100 +2356,100 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>96.2</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>0.1</v>
       </c>
-      <c r="D7">
-        <v>0.5</v>
-      </c>
       <c r="E7">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="G7">
-        <v>26.6</v>
+        <v>25.9</v>
       </c>
       <c r="H7">
-        <v>26.3</v>
+        <v>24.9</v>
       </c>
       <c r="I7">
-        <v>19.1</v>
+        <v>18.7</v>
       </c>
       <c r="J7">
-        <v>11.4</v>
+        <v>17.4</v>
       </c>
       <c r="K7">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="L7">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N7">
-        <v>36.3</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D8">
         <v>0.4</v>
       </c>
       <c r="E8">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="F8">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="G8">
-        <v>25.7</v>
+        <v>22.1</v>
       </c>
       <c r="H8">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="I8">
-        <v>18.6</v>
+        <v>21.2</v>
       </c>
       <c r="J8">
-        <v>12.8</v>
+        <v>19.4</v>
       </c>
       <c r="K8">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="L8">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="M8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>36.1</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2388,42 +2458,42 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E9">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F9">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>14</v>
+        <v>23.1</v>
       </c>
       <c r="H9">
-        <v>17.7</v>
+        <v>25.1</v>
       </c>
       <c r="I9">
-        <v>18.9</v>
+        <v>23.4</v>
       </c>
       <c r="J9">
-        <v>19.6</v>
+        <v>16.2</v>
       </c>
       <c r="K9">
-        <v>16.6</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="M9">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>16.6</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2432,86 +2502,86 @@
         <v>0</v>
       </c>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>0.2</v>
       </c>
-      <c r="E10">
-        <v>0.4</v>
-      </c>
       <c r="F10">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="G10">
-        <v>9.300000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="H10">
-        <v>17.5</v>
+        <v>18.8</v>
       </c>
       <c r="I10">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="J10">
-        <v>20.4</v>
+        <v>21.6</v>
       </c>
       <c r="K10">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="L10">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="M10">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>11.6</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0.1</v>
+      </c>
+      <c r="G11">
+        <v>0.9</v>
+      </c>
+      <c r="H11">
         <v>3</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0.5</v>
-      </c>
-      <c r="G11">
-        <v>4.7</v>
-      </c>
-      <c r="H11">
-        <v>7.5</v>
-      </c>
       <c r="I11">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
       <c r="J11">
-        <v>20.7</v>
+        <v>14.2</v>
       </c>
       <c r="K11">
-        <v>26.3</v>
+        <v>31.1</v>
       </c>
       <c r="L11">
-        <v>21</v>
+        <v>31.9</v>
       </c>
       <c r="M11">
-        <v>6.8</v>
+        <v>12.2</v>
       </c>
       <c r="N11">
-        <v>5.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2526,31 +2596,31 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G12">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="H12">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="I12">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
-        <v>11.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K12">
-        <v>20.5</v>
+        <v>26.6</v>
       </c>
       <c r="L12">
-        <v>38.4</v>
+        <v>37.8</v>
       </c>
       <c r="M12">
-        <v>20</v>
+        <v>17.6</v>
       </c>
       <c r="N12">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2576,22 +2646,22 @@
         <v>0.1</v>
       </c>
       <c r="H13">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="K13">
-        <v>6.3</v>
+        <v>8.6</v>
       </c>
       <c r="L13">
-        <v>21.2</v>
+        <v>19.9</v>
       </c>
       <c r="M13">
-        <v>67.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="N13">
         <v>0.1</v>
@@ -2604,10 +2674,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>40</v>
       </c>
@@ -2629,8 +2699,11 @@
       <c r="H1" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2644,24 +2717,27 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2">
+        <v>99.8</v>
+      </c>
+      <c r="I2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -2670,45 +2746,51 @@
         <v>100</v>
       </c>
       <c r="E3">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="F3">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G3">
         <v>100</v>
       </c>
-      <c r="G3">
-        <v>99.90000000000001</v>
-      </c>
       <c r="H3">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>99.8</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>21.5</v>
+        <v>24.5</v>
       </c>
       <c r="C4">
-        <v>71.8</v>
+        <v>71.2</v>
       </c>
       <c r="D4">
-        <v>84.39999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="E4">
-        <v>98.09999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="F4">
         <v>99.8</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="H4">
-        <v>99.59999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I4">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -2716,25 +2798,28 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>89.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="D5">
-        <v>89.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="E5">
-        <v>93.30000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="F5">
-        <v>88.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G5">
-        <v>93.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H5">
-        <v>96.39999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="I5">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -2742,129 +2827,144 @@
         <v>99.90000000000001</v>
       </c>
       <c r="C6">
-        <v>35.2</v>
+        <v>37.5</v>
       </c>
       <c r="D6">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="E6">
-        <v>65.5</v>
+        <v>67.30000000000001</v>
       </c>
       <c r="F6">
-        <v>89</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G6">
-        <v>96.7</v>
+        <v>97.2</v>
       </c>
       <c r="H6">
-        <v>96.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>99.2</v>
+      </c>
+      <c r="I6">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>2.8</v>
+      </c>
+      <c r="C7">
+        <v>72.8</v>
+      </c>
+      <c r="D7">
+        <v>20.4</v>
+      </c>
+      <c r="E7">
+        <v>22.2</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>11.6</v>
+      </c>
+      <c r="H7">
+        <v>30.6</v>
+      </c>
+      <c r="I7">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>33.3</v>
+      </c>
+      <c r="C8">
+        <v>14.6</v>
+      </c>
+      <c r="D8">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="E8">
+        <v>24.3</v>
+      </c>
+      <c r="F8">
+        <v>11.6</v>
+      </c>
+      <c r="G8">
+        <v>22</v>
+      </c>
+      <c r="H8">
+        <v>36.7</v>
+      </c>
+      <c r="I8">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B7">
-        <v>7.3</v>
-      </c>
-      <c r="C7">
-        <v>15.8</v>
-      </c>
-      <c r="D7">
-        <v>48.9</v>
-      </c>
-      <c r="E7">
-        <v>13.8</v>
-      </c>
-      <c r="F7">
-        <v>15.2</v>
-      </c>
-      <c r="G7">
-        <v>43.4</v>
-      </c>
-      <c r="H7">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
+      <c r="B9">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="C9">
+        <v>14.8</v>
+      </c>
+      <c r="D9">
+        <v>45.9</v>
+      </c>
+      <c r="E9">
+        <v>10.3</v>
+      </c>
+      <c r="F9">
+        <v>15.9</v>
+      </c>
+      <c r="G9">
+        <v>38.8</v>
+      </c>
+      <c r="H9">
+        <v>16.2</v>
+      </c>
+      <c r="I9">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>90.10000000000001</v>
-      </c>
-      <c r="C8">
-        <v>48.8</v>
-      </c>
-      <c r="D8">
+      <c r="B10">
         <v>91.40000000000001</v>
       </c>
-      <c r="E8">
-        <v>75.7</v>
-      </c>
-      <c r="F8">
-        <v>61.6</v>
-      </c>
-      <c r="G8">
-        <v>28.4</v>
-      </c>
-      <c r="H8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>35.6</v>
-      </c>
-      <c r="C9">
-        <v>14.3</v>
-      </c>
-      <c r="D9">
-        <v>8.4</v>
-      </c>
-      <c r="E9">
-        <v>24</v>
-      </c>
-      <c r="F9">
-        <v>13.6</v>
-      </c>
-      <c r="G9">
-        <v>19.9</v>
-      </c>
-      <c r="H9">
-        <v>17.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>3.9</v>
-      </c>
       <c r="C10">
-        <v>73.5</v>
+        <v>45.7</v>
       </c>
       <c r="D10">
-        <v>22</v>
+        <v>91.7</v>
       </c>
       <c r="E10">
-        <v>24.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F10">
-        <v>13.2</v>
+        <v>58.3</v>
       </c>
       <c r="G10">
-        <v>12.2</v>
+        <v>31.2</v>
       </c>
       <c r="H10">
-        <v>12.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>16.7</v>
+      </c>
+      <c r="I10">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -2881,21 +2981,24 @@
         <v>0.8</v>
       </c>
       <c r="F11">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="G11">
-        <v>5.1</v>
+        <v>5.899999999999999</v>
       </c>
       <c r="H11">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>1.4</v>
+      </c>
+      <c r="I11">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B12">
-        <v>0.8</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2904,42 +3007,48 @@
         <v>0.2</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F12">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="H12">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>1.1</v>
+      </c>
+      <c r="I12">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B13">
-        <v>40.9</v>
+        <v>38.8</v>
       </c>
       <c r="C13">
-        <v>50.7</v>
+        <v>53.1</v>
       </c>
       <c r="D13">
-        <v>44.4</v>
+        <v>49.3</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="F13">
-        <v>0.7000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H13">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2957,25 +3066,25 @@
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2986,25 +3095,25 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>99.48</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>119.43</v>
+        <v>118.78</v>
       </c>
       <c r="G2">
-        <v>0.438</v>
+        <v>0.469</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3012,28 +3121,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3">
-        <v>107.82</v>
+        <v>121.52</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>123.32</v>
+        <v>123.8</v>
       </c>
       <c r="G3">
-        <v>0.583</v>
+        <v>0.592</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3041,28 +3150,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4">
-        <v>125.34</v>
+        <v>96.64</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>121.27</v>
+        <v>120.3</v>
       </c>
       <c r="G4">
-        <v>0.5620000000000001</v>
+        <v>0.429</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3073,25 +3182,25 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5">
-        <v>109.43</v>
+        <v>113.62</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>118.17</v>
+        <v>119.37</v>
       </c>
       <c r="G5">
-        <v>0.479</v>
+        <v>0.51</v>
       </c>
       <c r="H5">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3099,28 +3208,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6">
-        <v>103.52</v>
+        <v>107.34</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>120.38</v>
+        <v>121.06</v>
       </c>
       <c r="G6">
-        <v>0.479</v>
+        <v>0.571</v>
       </c>
       <c r="H6">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3128,28 +3237,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7">
-        <v>118.68</v>
+        <v>106.73</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>117.46</v>
+        <v>116.35</v>
       </c>
       <c r="G7">
-        <v>0.521</v>
+        <v>0.49</v>
       </c>
       <c r="H7">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3157,28 +3266,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8">
+        <v>124.53</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>115.84</v>
+      </c>
+      <c r="G8">
+        <v>0.49</v>
+      </c>
+      <c r="H8">
+        <v>-0.6</v>
+      </c>
+      <c r="I8">
         <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8">
-        <v>102.37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8">
-        <v>116.7</v>
-      </c>
-      <c r="G8">
-        <v>0.5</v>
-      </c>
-      <c r="H8">
-        <v>-0.1</v>
-      </c>
-      <c r="I8">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3189,25 +3298,25 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9">
-        <v>118.79</v>
+        <v>120.25</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>118.69</v>
+        <v>119.43</v>
       </c>
       <c r="G9">
-        <v>0.583</v>
+        <v>0.633</v>
       </c>
       <c r="H9">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3215,28 +3324,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D10">
-        <v>126.64</v>
+        <v>140.1</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>115.42</v>
+        <v>112.46</v>
       </c>
       <c r="G10">
-        <v>0.521</v>
+        <v>0.408</v>
       </c>
       <c r="H10">
-        <v>-3</v>
+        <v>-3.1</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3244,28 +3353,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11">
-        <v>145.38</v>
+        <v>112.92</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11">
-        <v>111.67</v>
+        <v>113.42</v>
       </c>
       <c r="G11">
-        <v>0.417</v>
+        <v>0.469</v>
       </c>
       <c r="H11">
-        <v>-3.9</v>
+        <v>-6.9</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3273,28 +3382,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12">
-        <v>113.73</v>
+        <v>128.49</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>113.57</v>
+        <v>114.81</v>
       </c>
       <c r="G12">
-        <v>0.479</v>
+        <v>0.551</v>
       </c>
       <c r="H12">
-        <v>-4.9</v>
+        <v>-7.3</v>
       </c>
       <c r="I12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3305,25 +3414,25 @@
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13">
-        <v>135.6</v>
+        <v>132.99</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
       </c>
       <c r="F13">
-        <v>110.68</v>
+        <v>109.43</v>
       </c>
       <c r="G13">
-        <v>0.438</v>
+        <v>0.388</v>
       </c>
       <c r="H13">
-        <v>-6.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="I13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3341,45 +3450,45 @@
         <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D2">
-        <v>135.6033333333333</v>
+        <v>140.1028571428571</v>
       </c>
       <c r="E2">
-        <v>813.62</v>
+        <v>980.7199999999999</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -3388,39 +3497,39 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D3">
-        <v>145.3833333333333</v>
+        <v>132.9885714285714</v>
       </c>
       <c r="E3">
-        <v>872.3</v>
+        <v>930.92</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3434,254 +3543,254 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>125.3366666666667</v>
+        <v>121.5228571428571</v>
       </c>
       <c r="E4">
-        <v>752.02</v>
+        <v>850.66</v>
       </c>
       <c r="F4">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D5">
-        <v>126.6433333333333</v>
+        <v>124.5257142857143</v>
       </c>
       <c r="E5">
-        <v>759.86</v>
+        <v>871.6799999999999</v>
       </c>
       <c r="F5">
-        <v>96.89999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D6">
-        <v>118.6766666666667</v>
+        <v>128.4942857142857</v>
       </c>
       <c r="E6">
-        <v>712.0599999999999</v>
+        <v>899.46</v>
       </c>
       <c r="F6">
-        <v>96.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C7">
-        <v>0.6666666666666666</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D7">
-        <v>107.8166666666667</v>
+        <v>120.2542857142857</v>
       </c>
       <c r="E7">
-        <v>646.9000000000001</v>
+        <v>841.78</v>
       </c>
       <c r="F7">
-        <v>36.3</v>
+        <v>28.1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D8">
-        <v>113.7266666666667</v>
+        <v>107.3428571428572</v>
       </c>
       <c r="E8">
-        <v>682.36</v>
+        <v>751.4000000000001</v>
       </c>
       <c r="F8">
-        <v>36.1</v>
+        <v>26.8</v>
       </c>
       <c r="G8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C9">
-        <v>0.1666666666666667</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D9">
-        <v>118.7933333333333</v>
+        <v>113.6228571428571</v>
       </c>
       <c r="E9">
-        <v>712.76</v>
+        <v>795.36</v>
       </c>
       <c r="F9">
-        <v>16.6</v>
+        <v>26.8</v>
       </c>
       <c r="G9">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D10">
-        <v>109.4333333333333</v>
+        <v>112.92</v>
       </c>
       <c r="E10">
-        <v>656.6</v>
+        <v>790.4400000000001</v>
       </c>
       <c r="F10">
-        <v>11.6</v>
+        <v>19.4</v>
       </c>
       <c r="G10">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C11">
-        <v>0.3333333333333333</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D11">
-        <v>103.52</v>
+        <v>106.7257142857143</v>
       </c>
       <c r="E11">
-        <v>621.12</v>
+        <v>747.08</v>
       </c>
       <c r="F11">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>6.800000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
         <v>78</v>
       </c>
       <c r="C12">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D12">
-        <v>102.3666666666667</v>
+        <v>96.64</v>
       </c>
       <c r="E12">
-        <v>614.2</v>
+        <v>676.48</v>
       </c>
       <c r="F12">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="G12">
-        <v>20</v>
+        <v>17.6</v>
       </c>
       <c r="H12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3689,28 +3798,28 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>99.47666666666667</v>
+        <v>99.93428571428571</v>
       </c>
       <c r="E13">
-        <v>596.86</v>
+        <v>699.54</v>
       </c>
       <c r="F13">
         <v>0.1</v>
       </c>
       <c r="G13">
-        <v>67.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="H13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -3728,16 +3837,16 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3748,16 +3857,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3765,19 +3874,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3791,13 +3900,13 @@
         <v>64</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3805,19 +3914,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3828,16 +3937,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3845,19 +3954,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
         <v>58</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3865,19 +3974,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D8">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3885,19 +3994,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D9">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3905,19 +4014,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3928,16 +4037,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3945,19 +4054,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D12">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3968,16 +4077,16 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D13">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -3987,33 +4096,36 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>120</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4035,37 +4147,43 @@
       <c r="G2">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3">
+        <v>-2</v>
+      </c>
+      <c r="C3">
+        <v>-5</v>
+      </c>
+      <c r="D3">
+        <v>-5</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-      <c r="D3">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
       <c r="F3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -4087,37 +4205,43 @@
       <c r="G4">
         <v>12</v>
       </c>
-      <c r="H4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>-2</v>
-      </c>
-      <c r="C5">
-        <v>-5</v>
-      </c>
-      <c r="D5">
-        <v>-5</v>
-      </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
         <v>11</v>
       </c>
-      <c r="H5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -4139,115 +4263,130 @@
       <c r="G6">
         <v>8</v>
       </c>
-      <c r="H6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>-1</v>
+      </c>
+      <c r="E7">
+        <v>-6</v>
+      </c>
+      <c r="F7">
+        <v>-5</v>
+      </c>
+      <c r="G7">
+        <v>-4</v>
+      </c>
+      <c r="H7">
         <v>3</v>
       </c>
-      <c r="B7">
-        <v>-4</v>
-      </c>
-      <c r="C7">
-        <v>-4</v>
-      </c>
-      <c r="D7">
-        <v>-5</v>
-      </c>
-      <c r="E7">
+      <c r="I7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>-3</v>
+      </c>
+      <c r="D8">
+        <v>-9</v>
+      </c>
+      <c r="E8">
+        <v>-12</v>
+      </c>
+      <c r="F8">
+        <v>-12</v>
+      </c>
+      <c r="G8">
+        <v>-9</v>
+      </c>
+      <c r="H8">
         <v>-2</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-      <c r="H7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
+      <c r="I8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D8">
-        <v>-1</v>
-      </c>
-      <c r="E8">
-        <v>-6</v>
-      </c>
-      <c r="F8">
-        <v>-5</v>
-      </c>
-      <c r="G8">
-        <v>-4</v>
-      </c>
-      <c r="H8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="B9">
         <v>-4</v>
       </c>
       <c r="C9">
+        <v>-15</v>
+      </c>
+      <c r="D9">
+        <v>-12</v>
+      </c>
+      <c r="E9">
+        <v>-12</v>
+      </c>
+      <c r="F9">
+        <v>-11</v>
+      </c>
+      <c r="G9">
+        <v>-10</v>
+      </c>
+      <c r="H9">
         <v>-5</v>
       </c>
-      <c r="D9">
-        <v>-7</v>
-      </c>
-      <c r="E9">
+      <c r="I9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>-4</v>
+      </c>
+      <c r="C10">
+        <v>-4</v>
+      </c>
+      <c r="D10">
         <v>-5</v>
       </c>
-      <c r="F9">
+      <c r="E10">
         <v>-2</v>
       </c>
-      <c r="G9">
-        <v>-8</v>
-      </c>
-      <c r="H9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>-3</v>
-      </c>
-      <c r="D10">
-        <v>-9</v>
-      </c>
-      <c r="E10">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+      <c r="H10">
         <v>-12</v>
       </c>
-      <c r="F10">
-        <v>-12</v>
-      </c>
-      <c r="G10">
-        <v>-9</v>
-      </c>
-      <c r="H10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -4269,37 +4408,43 @@
       <c r="G11">
         <v>-10</v>
       </c>
-      <c r="H11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="H11">
+        <v>-13</v>
+      </c>
+      <c r="I11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B12">
         <v>-4</v>
       </c>
       <c r="C12">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="D12">
-        <v>-12</v>
+        <v>-7</v>
       </c>
       <c r="E12">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="F12">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="G12">
-        <v>-10</v>
-      </c>
-      <c r="H12" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>-8</v>
+      </c>
+      <c r="H12">
+        <v>-17</v>
+      </c>
+      <c r="I12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
@@ -4321,8 +4466,11 @@
       <c r="G13">
         <v>-17</v>
       </c>
-      <c r="H13" t="s">
-        <v>103</v>
+      <c r="H13">
+        <v>-21</v>
+      </c>
+      <c r="I13" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Family Fantasy 2026.xlsx
+++ b/data/leagues/Family Fantasy 2026.xlsx
@@ -259,52 +259,52 @@
     <t>6-1</t>
   </si>
   <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
     <t>2-5</t>
   </si>
   <si>
-    <t>4-3</t>
-  </si>
-  <si>
-    <t>3-4</t>
-  </si>
-  <si>
     <t>1-6</t>
   </si>
   <si>
     <t>0-7</t>
   </si>
   <si>
-    <t>10.3-3.6</t>
-  </si>
-  <si>
     <t>10.4-3.5-0.1</t>
   </si>
   <si>
     <t>10.3-3.6-0.1</t>
   </si>
   <si>
+    <t>9.5-4.4-0.1</t>
+  </si>
+  <si>
+    <t>10.2-3.7-0.1</t>
+  </si>
+  <si>
     <t>10.1-3.8-0.1</t>
   </si>
   <si>
-    <t>9.4-4.5-0.1</t>
+    <t>6.0-7.9-0.1</t>
+  </si>
+  <si>
+    <t>6.2-7.7-0.1</t>
   </si>
   <si>
     <t>5.6-8.3-0.1</t>
   </si>
   <si>
-    <t>6.2-7.7-0.1</t>
-  </si>
-  <si>
-    <t>6.0-7.9-0.1</t>
-  </si>
-  <si>
-    <t>5.4-8.5-0.1</t>
+    <t>5.5-8.5-0.1</t>
   </si>
   <si>
     <t>3.7-10.2-0.1</t>
   </si>
   <si>
-    <t>3.9-10.1-0.1</t>
+    <t>3.8-10.1-0.1</t>
   </si>
   <si>
     <t>2.1-11.8-0.1</t>
@@ -316,10 +316,10 @@
     <t>10-4</t>
   </si>
   <si>
-    <t>9-5</t>
-  </si>
-  <si>
     <t>6-8</t>
+  </si>
+  <si>
+    <t>5-9</t>
   </si>
   <si>
     <t>4-10</t>
@@ -2141,25 +2141,25 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>33.7</v>
+        <v>25</v>
       </c>
       <c r="C2">
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="D2">
-        <v>18.3</v>
+        <v>23.9</v>
       </c>
       <c r="E2">
-        <v>13.3</v>
+        <v>15.7</v>
       </c>
       <c r="F2">
         <v>8.1</v>
       </c>
       <c r="G2">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -2185,25 +2185,25 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>23.5</v>
+        <v>32.2</v>
       </c>
       <c r="C3">
-        <v>28.9</v>
+        <v>24.8</v>
       </c>
       <c r="D3">
-        <v>23.6</v>
+        <v>20.4</v>
       </c>
       <c r="E3">
-        <v>16.1</v>
+        <v>14.6</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="G3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0.1</v>
@@ -2229,31 +2229,31 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>19.4</v>
+        <v>8.6</v>
       </c>
       <c r="C4">
-        <v>17.1</v>
+        <v>13.6</v>
       </c>
       <c r="D4">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="E4">
-        <v>22.6</v>
+        <v>24.2</v>
       </c>
       <c r="F4">
-        <v>19.7</v>
+        <v>30.3</v>
       </c>
       <c r="G4">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2273,31 +2273,31 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B5">
+        <v>19.5</v>
+      </c>
+      <c r="C5">
+        <v>15.2</v>
+      </c>
+      <c r="D5">
         <v>16.2</v>
       </c>
-      <c r="C5">
-        <v>16.6</v>
-      </c>
-      <c r="D5">
-        <v>20.9</v>
-      </c>
       <c r="E5">
-        <v>20</v>
+        <v>21.8</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>24.2</v>
       </c>
       <c r="G5">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="H5">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2312,39 +2312,39 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6">
-        <v>7.2</v>
+        <v>14.7</v>
       </c>
       <c r="C6">
-        <v>11.8</v>
+        <v>19.2</v>
       </c>
       <c r="D6">
-        <v>17.4</v>
+        <v>19.9</v>
       </c>
       <c r="E6">
-        <v>26.1</v>
+        <v>21.5</v>
       </c>
       <c r="F6">
-        <v>32.1</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="H6">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="I6">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -2356,51 +2356,51 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>98.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E7">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F7">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="G7">
-        <v>25.9</v>
+        <v>25.3</v>
       </c>
       <c r="H7">
-        <v>24.9</v>
+        <v>26.2</v>
       </c>
       <c r="I7">
-        <v>18.7</v>
+        <v>20.7</v>
       </c>
       <c r="J7">
-        <v>17.4</v>
+        <v>14.8</v>
       </c>
       <c r="K7">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="L7">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M7">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="N7">
-        <v>28.1</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -2411,45 +2411,45 @@
         <v>0</v>
       </c>
       <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>0.1</v>
       </c>
-      <c r="D8">
-        <v>0.4</v>
-      </c>
       <c r="E8">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F8">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="G8">
-        <v>22.1</v>
+        <v>23.2</v>
       </c>
       <c r="H8">
-        <v>24.1</v>
+        <v>23.2</v>
       </c>
       <c r="I8">
-        <v>21.2</v>
+        <v>22.8</v>
       </c>
       <c r="J8">
-        <v>19.4</v>
+        <v>18.6</v>
       </c>
       <c r="K8">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="L8">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
-        <v>26.8</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2458,37 +2458,37 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="G9">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="H9">
-        <v>25.1</v>
+        <v>24.3</v>
       </c>
       <c r="I9">
-        <v>23.4</v>
+        <v>21.5</v>
       </c>
       <c r="J9">
         <v>16.2</v>
       </c>
       <c r="K9">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="L9">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N9">
-        <v>26.8</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2505,34 +2505,34 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F10">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G10">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="H10">
-        <v>18.8</v>
+        <v>19.8</v>
       </c>
       <c r="I10">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="J10">
-        <v>21.6</v>
+        <v>23.2</v>
       </c>
       <c r="K10">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="L10">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="M10">
         <v>1</v>
       </c>
       <c r="N10">
-        <v>19.4</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2555,28 +2555,28 @@
         <v>0.1</v>
       </c>
       <c r="G11">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="I11">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="K11">
-        <v>31.1</v>
+        <v>33</v>
       </c>
       <c r="L11">
-        <v>31.9</v>
+        <v>29.5</v>
       </c>
       <c r="M11">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2596,28 +2596,28 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H12">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="I12">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="J12">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="K12">
-        <v>26.6</v>
+        <v>23.9</v>
       </c>
       <c r="L12">
-        <v>37.8</v>
+        <v>40.7</v>
       </c>
       <c r="M12">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="N12">
         <v>0.5</v>
@@ -2649,19 +2649,19 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J13">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="L13">
-        <v>19.9</v>
+        <v>20.4</v>
       </c>
       <c r="M13">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N13">
         <v>0.1</v>
@@ -2726,10 +2726,10 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2755,10 +2755,10 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="I3">
-        <v>100</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2784,7 +2784,7 @@
         <v>99.7</v>
       </c>
       <c r="H4">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="I4">
         <v>99.7</v>
@@ -2813,7 +2813,7 @@
         <v>91.90000000000001</v>
       </c>
       <c r="H5">
-        <v>98.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="I5">
         <v>99.7</v>
@@ -2842,7 +2842,7 @@
         <v>97.2</v>
       </c>
       <c r="H6">
-        <v>99.2</v>
+        <v>98.2</v>
       </c>
       <c r="I6">
         <v>98.90000000000001</v>
@@ -2871,68 +2871,68 @@
         <v>11.6</v>
       </c>
       <c r="H7">
-        <v>30.6</v>
+        <v>34.8</v>
       </c>
       <c r="I7">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>33.3</v>
+        <v>8.200000000000001</v>
       </c>
       <c r="C8">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="D8">
-        <v>8.200000000000001</v>
+        <v>45.9</v>
       </c>
       <c r="E8">
-        <v>24.3</v>
+        <v>10.3</v>
       </c>
       <c r="F8">
-        <v>11.6</v>
+        <v>15.9</v>
       </c>
       <c r="G8">
-        <v>22</v>
+        <v>38.8</v>
       </c>
       <c r="H8">
-        <v>36.7</v>
+        <v>17.6</v>
       </c>
       <c r="I8">
-        <v>26.9</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9">
+        <v>33.3</v>
+      </c>
+      <c r="C9">
+        <v>14.6</v>
+      </c>
+      <c r="D9">
         <v>8.200000000000001</v>
       </c>
-      <c r="C9">
-        <v>14.8</v>
-      </c>
-      <c r="D9">
-        <v>45.9</v>
-      </c>
       <c r="E9">
-        <v>10.3</v>
+        <v>24.3</v>
       </c>
       <c r="F9">
-        <v>15.9</v>
+        <v>11.6</v>
       </c>
       <c r="G9">
-        <v>38.8</v>
+        <v>22</v>
       </c>
       <c r="H9">
-        <v>16.2</v>
+        <v>32.1</v>
       </c>
       <c r="I9">
-        <v>23.3</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2958,68 +2958,68 @@
         <v>31.2</v>
       </c>
       <c r="H10">
-        <v>16.7</v>
+        <v>16.3</v>
       </c>
       <c r="I10">
-        <v>19.8</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B11">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <v>0.2</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
       <c r="E11">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="F11">
-        <v>15.2</v>
+        <v>5.2</v>
       </c>
       <c r="G11">
-        <v>5.899999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="H11">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I11">
-        <v>0.8</v>
+        <v>0.7000000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B12">
-        <v>0.8999999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="F12">
-        <v>5.2</v>
+        <v>15.2</v>
       </c>
       <c r="G12">
-        <v>1.6</v>
+        <v>5.899999999999999</v>
       </c>
       <c r="H12">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="I12">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3476,7 +3476,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
@@ -3485,10 +3485,10 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="D2">
-        <v>140.1028571428571</v>
+        <v>132.9885714285714</v>
       </c>
       <c r="E2">
-        <v>980.7199999999999</v>
+        <v>930.92</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
@@ -3514,10 +3514,10 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="D3">
-        <v>132.9885714285714</v>
+        <v>140.1028571428571</v>
       </c>
       <c r="E3">
-        <v>930.92</v>
+        <v>980.7199999999999</v>
       </c>
       <c r="F3">
         <v>99.90000000000001</v>
@@ -3529,24 +3529,24 @@
         <v>84</v>
       </c>
       <c r="I3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D4">
-        <v>121.5228571428571</v>
+        <v>128.4942857142857</v>
       </c>
       <c r="E4">
-        <v>850.66</v>
+        <v>899.46</v>
       </c>
       <c r="F4">
         <v>99.40000000000001</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>124.5257142857143</v>
+        <v>121.5228571428571</v>
       </c>
       <c r="E5">
-        <v>871.6799999999999</v>
+        <v>850.66</v>
       </c>
       <c r="F5">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -3592,22 +3592,22 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D6">
-        <v>128.4942857142857</v>
+        <v>124.5257142857143</v>
       </c>
       <c r="E6">
-        <v>899.46</v>
+        <v>871.6799999999999</v>
       </c>
       <c r="F6">
-        <v>98.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3616,36 +3616,36 @@
         <v>87</v>
       </c>
       <c r="I6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7">
-        <v>0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D7">
-        <v>120.2542857142857</v>
+        <v>113.6228571428571</v>
       </c>
       <c r="E7">
-        <v>841.78</v>
+        <v>795.36</v>
       </c>
       <c r="F7">
-        <v>28.1</v>
+        <v>29.9</v>
       </c>
       <c r="G7">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H7" t="s">
         <v>88</v>
       </c>
       <c r="I7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3665,7 +3665,7 @@
         <v>751.4000000000001</v>
       </c>
       <c r="F8">
-        <v>26.8</v>
+        <v>26.4</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -3674,30 +3674,30 @@
         <v>89</v>
       </c>
       <c r="I8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
         <v>80</v>
       </c>
       <c r="C9">
-        <v>0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D9">
-        <v>113.6228571428571</v>
+        <v>120.2542857142857</v>
       </c>
       <c r="E9">
-        <v>795.36</v>
+        <v>841.78</v>
       </c>
       <c r="F9">
-        <v>26.8</v>
+        <v>26.1</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H9" t="s">
         <v>90</v>
@@ -3711,7 +3711,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C10">
         <v>0.2857142857142857</v>
@@ -3723,7 +3723,7 @@
         <v>790.4400000000001</v>
       </c>
       <c r="F10">
-        <v>19.4</v>
+        <v>18.3</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -3732,7 +3732,7 @@
         <v>91</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3752,10 +3752,10 @@
         <v>747.08</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G11">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="H11" t="s">
         <v>92</v>
@@ -3769,7 +3769,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C12">
         <v>0.2857142857142857</v>
@@ -3784,7 +3784,7 @@
         <v>0.5</v>
       </c>
       <c r="G12">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="H12" t="s">
         <v>93</v>
@@ -3813,7 +3813,7 @@
         <v>0.1</v>
       </c>
       <c r="G13">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H13" t="s">
         <v>94</v>
